--- a/tutorial/ecoli/experiments/Δzwf_ecoli.xlsx
+++ b/tutorial/ecoli/experiments/Δzwf_ecoli.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28623"/>
+  <fileVersion appName="libxl" lastEdited="7" lowestEdited="6" rupBuild="4.6.0"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="6150" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="6642" uniqueCount="63">
   <si>
     <t>mu</t>
   </si>
@@ -611,7 +611,7 @@
         <v>49</v>
       </c>
       <c r="B2" s="0">
-        <v>8.0082081154324491</v>
+        <v>8.0082081154324492</v>
       </c>
       <c r="C2" s="0" t="s">
         <v>52</v>
@@ -2106,7 +2106,7 @@
         <v>0.60438667749796915</v>
       </c>
       <c r="Q2" s="0">
-        <v>0.33651438560022678</v>
+        <v>0.33651438560022679</v>
       </c>
       <c r="R2" s="0">
         <v>0.34114851485148517</v>
@@ -2121,7 +2121,7 @@
         <v>0.15994532937365011</v>
       </c>
       <c r="V2" s="0">
-        <v>0.15950191540742722</v>
+        <v>0.15950191540742723</v>
       </c>
       <c r="W2" s="0">
         <v>0.17215333453636153</v>
@@ -2160,7 +2160,7 @@
         <v>0.14120977765502002</v>
       </c>
       <c r="AI2" s="0">
-        <v>0.15804938271604937</v>
+        <v>0.15804938271604938</v>
       </c>
       <c r="AJ2" s="0">
         <v>0.70762500222098945</v>
@@ -2219,7 +2219,7 @@
         <v>0.42493622147682714</v>
       </c>
       <c r="R3" s="0">
-        <v>0.4282310231023102</v>
+        <v>0.42823102310231021</v>
       </c>
       <c r="S3" s="0">
         <v>0.44746430491993988</v>
@@ -2273,7 +2273,7 @@
         <v>0.35787654320987655</v>
       </c>
       <c r="AJ3" s="0">
-        <v>0.19647168682667004</v>
+        <v>0.19647168682667005</v>
       </c>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="4" x14ac:dyDescent="0.3">
@@ -2326,7 +2326,7 @@
         <v>0.072298943948009745</v>
       </c>
       <c r="Q4" s="0">
-        <v>0.15923961827372798</v>
+        <v>0.15923961827372799</v>
       </c>
       <c r="R4" s="0">
         <v>0.15503630363036303</v>
@@ -2350,7 +2350,7 @@
         <v>0.075659786567831816</v>
       </c>
       <c r="Y4" s="0">
-        <v>0.21549490933188747</v>
+        <v>0.21549490933188748</v>
       </c>
       <c r="Z4" s="0">
         <v>0.19633395168646423</v>
@@ -2614,7 +2614,7 @@
         <v>0.001023941422191945</v>
       </c>
       <c r="C7" s="0">
-        <v>0.00081517006350785277</v>
+        <v>0.00081517006350785278</v>
       </c>
       <c r="D7" s="0">
         <v>0.00050781063439291291</v>
@@ -2710,7 +2710,7 @@
         <v>0.014776964507664686</v>
       </c>
       <c r="AI7" s="0">
-        <v>0.0093827160493827159</v>
+        <v>0.009382716049382716</v>
       </c>
       <c r="AJ7" s="0">
         <v>0.0032377090444612473</v>
@@ -3224,7 +3224,7 @@
         <v>0.00045623667670911767</v>
       </c>
       <c r="W12" s="0">
-        <v>0.003273955298909541</v>
+        <v>0.0032739552989095411</v>
       </c>
       <c r="X12" s="0">
         <v>0</v>
@@ -3334,7 +3334,7 @@
         <v>0.0010068671485994321</v>
       </c>
       <c r="W13" s="0">
-        <v>0.033884148384934649</v>
+        <v>0.03388414838493465</v>
       </c>
       <c r="X13" s="0">
         <v>0</v>
@@ -3497,38 +3497,38 @@
   <sheetFormatPr xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5.85546875" customWidth="true"/>
-    <col min="2" max="2" width="16.42578125" customWidth="true"/>
-    <col min="3" max="3" width="16.42578125" customWidth="true"/>
-    <col min="4" max="4" width="16.28515625" customWidth="true"/>
-    <col min="5" max="5" width="16.28515625" customWidth="true"/>
-    <col min="6" max="6" width="16.42578125" customWidth="true"/>
-    <col min="7" max="7" width="16.28515625" customWidth="true"/>
-    <col min="8" max="8" width="16.42578125" customWidth="true"/>
-    <col min="9" max="9" width="16.28515625" customWidth="true"/>
-    <col min="10" max="10" width="16.28515625" customWidth="true"/>
-    <col min="11" max="11" width="16.28515625" customWidth="true"/>
-    <col min="12" max="12" width="16.28515625" customWidth="true"/>
-    <col min="13" max="13" width="15.7109375" customWidth="true"/>
+    <col min="2" max="2" width="15.7109375" customWidth="true"/>
+    <col min="3" max="3" width="14.7109375" customWidth="true"/>
+    <col min="4" max="4" width="13.7109375" customWidth="true"/>
+    <col min="5" max="5" width="15.7109375" customWidth="true"/>
+    <col min="6" max="6" width="15.7109375" customWidth="true"/>
+    <col min="7" max="7" width="13.7109375" customWidth="true"/>
+    <col min="8" max="8" width="13.7109375" customWidth="true"/>
+    <col min="9" max="9" width="15.5703125" customWidth="true"/>
+    <col min="10" max="10" width="15.7109375" customWidth="true"/>
+    <col min="11" max="11" width="15.5703125" customWidth="true"/>
+    <col min="12" max="12" width="15.7109375" customWidth="true"/>
+    <col min="13" max="13" width="16.42578125" customWidth="true"/>
     <col min="14" max="14" width="16.28515625" customWidth="true"/>
     <col min="15" max="15" width="16.42578125" customWidth="true"/>
     <col min="16" max="16" width="16.42578125" customWidth="true"/>
-    <col min="17" max="17" width="16.42578125" customWidth="true"/>
+    <col min="17" max="17" width="16.28515625" customWidth="true"/>
     <col min="18" max="18" width="16.42578125" customWidth="true"/>
-    <col min="19" max="19" width="16.42578125" customWidth="true"/>
-    <col min="20" max="20" width="16.42578125" customWidth="true"/>
-    <col min="21" max="21" width="16.28515625" customWidth="true"/>
-    <col min="22" max="22" width="16.42578125" customWidth="true"/>
+    <col min="19" max="19" width="15.42578125" customWidth="true"/>
+    <col min="20" max="20" width="14.7109375" customWidth="true"/>
+    <col min="21" max="21" width="15.7109375" customWidth="true"/>
+    <col min="22" max="22" width="16.28515625" customWidth="true"/>
     <col min="23" max="23" width="16.28515625" customWidth="true"/>
-    <col min="24" max="24" width="16.42578125" customWidth="true"/>
-    <col min="25" max="25" width="16.42578125" customWidth="true"/>
-    <col min="26" max="26" width="16.42578125" customWidth="true"/>
-    <col min="27" max="27" width="16.42578125" customWidth="true"/>
-    <col min="28" max="28" width="16.42578125" customWidth="true"/>
-    <col min="29" max="29" width="16.28515625" customWidth="true"/>
+    <col min="24" max="24" width="15.7109375" customWidth="true"/>
+    <col min="25" max="25" width="15.5703125" customWidth="true"/>
+    <col min="26" max="26" width="14.7109375" customWidth="true"/>
+    <col min="27" max="27" width="13.7109375" customWidth="true"/>
+    <col min="28" max="28" width="13.7109375" customWidth="true"/>
+    <col min="29" max="29" width="14.7109375" customWidth="true"/>
     <col min="30" max="30" width="16.42578125" customWidth="true"/>
-    <col min="31" max="31" width="16.28515625" customWidth="true"/>
-    <col min="32" max="32" width="16.28515625" customWidth="true"/>
-    <col min="33" max="33" width="16.42578125" customWidth="true"/>
+    <col min="31" max="31" width="15.7109375" customWidth="true"/>
+    <col min="32" max="32" width="12.7109375" customWidth="true"/>
+    <col min="33" max="33" width="16.28515625" customWidth="true"/>
     <col min="34" max="34" width="16.42578125" customWidth="true"/>
     <col min="35" max="35" width="16.42578125" customWidth="true"/>
     <col min="36" max="36" width="16.42578125" customWidth="true"/>
@@ -3649,109 +3649,109 @@
         <v>36</v>
       </c>
       <c r="B2" s="0">
-        <v>0.51350984969669766</v>
+        <v>0.51341278063261953</v>
       </c>
       <c r="C2" s="0">
-        <v>0.51509103202351647</v>
+        <v>0.51508455763192529</v>
       </c>
       <c r="D2" s="0">
-        <v>0.48768279867162884</v>
+        <v>0.49086915129061254</v>
       </c>
       <c r="E2" s="0">
-        <v>0.2697211426300089</v>
+        <v>0.2697251881976197</v>
       </c>
       <c r="F2" s="0">
-        <v>0.26672805677276828</v>
+        <v>0.26671243942007955</v>
       </c>
       <c r="G2" s="0">
-        <v>0.265531040324821</v>
+        <v>0.26572855277509816</v>
       </c>
       <c r="H2" s="0">
-        <v>0.89823861276613315</v>
+        <v>0.89839430616516691</v>
       </c>
       <c r="I2" s="0">
-        <v>0.14746848215639852</v>
+        <v>0.14748822635653811</v>
       </c>
       <c r="J2" s="0">
-        <v>0.14453639195460671</v>
+        <v>0.14458873349605683</v>
       </c>
       <c r="K2" s="0">
-        <v>0.23137046096845612</v>
+        <v>0.23135594300118856</v>
       </c>
       <c r="L2" s="0">
-        <v>0.22937872810941309</v>
+        <v>0.22949606243216531</v>
       </c>
       <c r="M2" s="0">
-        <v>0.33060292400153218</v>
+        <v>0.33060288254597392</v>
       </c>
       <c r="N2" s="0">
-        <v>0.23584221139782066</v>
+        <v>0.23584220529044581</v>
       </c>
       <c r="O2" s="0">
-        <v>0.25620137346246097</v>
+        <v>0.256201393512067</v>
       </c>
       <c r="P2" s="0">
-        <v>0.83710558421292458</v>
+        <v>0.83710572740979106</v>
       </c>
       <c r="Q2" s="0">
-        <v>0.52383204457829935</v>
+        <v>0.52377008067123143</v>
       </c>
       <c r="R2" s="0">
-        <v>0.52408687404978604</v>
+        <v>0.52380586118021522</v>
       </c>
       <c r="S2" s="0">
-        <v>0.52491363200886909</v>
+        <v>0.52516283021150545</v>
       </c>
       <c r="T2" s="0">
-        <v>0.98527023887271659</v>
+        <v>0.98807909320410126</v>
       </c>
       <c r="U2" s="0">
-        <v>0.22872562199731555</v>
+        <v>0.22874005736512776</v>
       </c>
       <c r="V2" s="0">
-        <v>0.22510653461395255</v>
+        <v>0.22544523392496893</v>
       </c>
       <c r="W2" s="0">
-        <v>0.21856185951950505</v>
+        <v>0.2270189040434559</v>
       </c>
       <c r="X2" s="0">
-        <v>0.98586456387176291</v>
+        <v>0.98603936660245373</v>
       </c>
       <c r="Y2" s="0">
-        <v>0.41588526817398325</v>
+        <v>0.41584700820439163</v>
       </c>
       <c r="Z2" s="0">
-        <v>0.44780287230929638</v>
+        <v>0.44775810082403611</v>
       </c>
       <c r="AA2" s="0">
-        <v>0.44040452996825774</v>
+        <v>0.44207487918355831</v>
       </c>
       <c r="AB2" s="0">
-        <v>0.70526061339160362</v>
+        <v>0.70595387404117616</v>
       </c>
       <c r="AC2" s="0">
-        <v>0.23290240417291405</v>
+        <v>0.23289747774040234</v>
       </c>
       <c r="AD2" s="0">
-        <v>0.24982140037055581</v>
+        <v>0.24975365674860758</v>
       </c>
       <c r="AE2" s="0">
-        <v>0.25077688976154311</v>
+        <v>0.250819288823454</v>
       </c>
       <c r="AF2" s="0">
-        <v>0.71583387341317006</v>
+        <v>0.72510567626033962</v>
       </c>
       <c r="AG2" s="0">
-        <v>0.22930038862899876</v>
+        <v>0.22930045951880537</v>
       </c>
       <c r="AH2" s="0">
-        <v>0.23154383934020081</v>
+        <v>0.23152834534754155</v>
       </c>
       <c r="AI2" s="0">
-        <v>0.23314410272137392</v>
+        <v>0.23314410309881009</v>
       </c>
       <c r="AJ2" s="0">
-        <v>0.98009596580633718</v>
+        <v>0.98009598321372227</v>
       </c>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="3" x14ac:dyDescent="0.3">
@@ -3759,109 +3759,109 @@
         <v>37</v>
       </c>
       <c r="B3" s="0">
-        <v>0.48060438926319449</v>
+        <v>0.47537204545573625</v>
       </c>
       <c r="C3" s="0">
-        <v>0.48584642238211928</v>
+        <v>0.48064182420140078</v>
       </c>
       <c r="D3" s="0">
-        <v>0.46671589648108175</v>
+        <v>0.46473877026554317</v>
       </c>
       <c r="E3" s="0">
-        <v>0.49925913127601268</v>
+        <v>0.49392446687029762</v>
       </c>
       <c r="F3" s="0">
-        <v>0.49682733183961764</v>
+        <v>0.4914825006204247</v>
       </c>
       <c r="G3" s="0">
-        <v>0.48990291165977345</v>
+        <v>0.48502146041666405</v>
       </c>
       <c r="H3" s="0">
-        <v>0.077060571391607061</v>
+        <v>0.076249237411939355</v>
       </c>
       <c r="I3" s="0">
-        <v>0.39236312388777522</v>
+        <v>0.38821680891813837</v>
       </c>
       <c r="J3" s="0">
-        <v>0.38459142502818983</v>
+        <v>0.38061408018281995</v>
       </c>
       <c r="K3" s="0">
-        <v>0.46652086827015821</v>
+        <v>0.46150013508450244</v>
       </c>
       <c r="L3" s="0">
-        <v>0.45949197649063633</v>
+        <v>0.45480794174273992</v>
       </c>
       <c r="M3" s="0">
-        <v>0.27344687220186642</v>
+        <v>0.27052095674765037</v>
       </c>
       <c r="N3" s="0">
-        <v>0.471683685391519</v>
+        <v>0.46663665787379671</v>
       </c>
       <c r="O3" s="0">
-        <v>0.46947854181598037</v>
+        <v>0.46445515776551383</v>
       </c>
       <c r="P3" s="0">
-        <v>0.17203393408855877</v>
+        <v>0.17019320010737729</v>
       </c>
       <c r="Q3" s="0">
-        <v>0.47968379846891873</v>
+        <v>0.47449504733403836</v>
       </c>
       <c r="R3" s="0">
-        <v>0.48185702580014739</v>
+        <v>0.47644555074958367</v>
       </c>
       <c r="S3" s="0">
-        <v>0.48083348596509817</v>
+        <v>0.47591439669475061</v>
       </c>
       <c r="T3" s="0">
-        <v>0.0094918607778422467</v>
+        <v>0.0094170681664663032</v>
       </c>
       <c r="U3" s="0">
-        <v>0.46034885867999065</v>
+        <v>0.45545186862882708</v>
       </c>
       <c r="V3" s="0">
-        <v>0.45955969075096109</v>
+        <v>0.45532646513521857</v>
       </c>
       <c r="W3" s="0">
-        <v>0.440783209914068</v>
+        <v>0.45294002327699989</v>
       </c>
       <c r="X3" s="0">
-        <v>0.01324562165276875</v>
+        <v>0.013106216940277107</v>
       </c>
       <c r="Y3" s="0">
-        <v>0.4797958871101124</v>
+        <v>0.47461840389104387</v>
       </c>
       <c r="Z3" s="0">
-        <v>0.48633451411275502</v>
+        <v>0.48108263119532724</v>
       </c>
       <c r="AA3" s="0">
-        <v>0.47750182942834379</v>
+        <v>0.47418423202749999</v>
       </c>
       <c r="AB3" s="0">
-        <v>0.28357676248827979</v>
+        <v>0.28081826020840456</v>
       </c>
       <c r="AC3" s="0">
-        <v>0.46358774991980917</v>
+        <v>0.45861765995050197</v>
       </c>
       <c r="AD3" s="0">
-        <v>0.48109172278198631</v>
+        <v>0.47581498045448545</v>
       </c>
       <c r="AE3" s="0">
-        <v>0.47881321289088608</v>
+        <v>0.47376999866892672</v>
       </c>
       <c r="AF3" s="0">
-        <v>0.24178613446806527</v>
+        <v>0.24229723634398456</v>
       </c>
       <c r="AG3" s="0">
-        <v>0.46014911078671988</v>
+        <v>0.45522565603742954</v>
       </c>
       <c r="AH3" s="0">
-        <v>0.45921196181121793</v>
+        <v>0.45426799397849876</v>
       </c>
       <c r="AI3" s="0">
-        <v>0.4515275305243498</v>
+        <v>0.446696186670894</v>
       </c>
       <c r="AJ3" s="0">
-        <v>0.015111063588680411</v>
+        <v>0.014949375473795866</v>
       </c>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="4" x14ac:dyDescent="0.3">
@@ -3869,109 +3869,109 @@
         <v>38</v>
       </c>
       <c r="B4" s="0">
-        <v>0.0055660302950550789</v>
+        <v>0.010533005633545634</v>
       </c>
       <c r="C4" s="0">
-        <v>-0.00088816533039356028</v>
+        <v>0.0042736181666740919</v>
       </c>
       <c r="D4" s="0">
-        <v>0.040015237471749815</v>
+        <v>0.044392078443844262</v>
       </c>
       <c r="E4" s="0">
-        <v>0.2296640534620977</v>
+        <v>0.23006390017610839</v>
       </c>
       <c r="F4" s="0">
-        <v>0.23704044222774792</v>
+        <v>0.23724019460901327</v>
       </c>
       <c r="G4" s="0">
-        <v>0.23196386563668903</v>
+        <v>0.23238499726050144</v>
       </c>
       <c r="H4" s="0">
-        <v>0.025069963614116866</v>
+        <v>0.025356456422893775</v>
       </c>
       <c r="I4" s="0">
-        <v>0.35571789771032358</v>
+        <v>0.35234679316177953</v>
       </c>
       <c r="J4" s="0">
-        <v>0.35592235108121728</v>
+        <v>0.35254508103682564</v>
       </c>
       <c r="K4" s="0">
-        <v>0.26941460196782718</v>
+        <v>0.26860148089353481</v>
       </c>
       <c r="L4" s="0">
-        <v>0.27087818759049692</v>
+        <v>0.27011446540261075</v>
       </c>
       <c r="M4" s="0">
-        <v>0.15185654758740413</v>
+        <v>0.15151875912581259</v>
       </c>
       <c r="N4" s="0">
-        <v>0.26315329732924203</v>
+        <v>0.26254495075708656</v>
       </c>
       <c r="O4" s="0">
-        <v>0.2468357622381071</v>
+        <v>0.24655142624623527</v>
       </c>
       <c r="P4" s="0">
-        <v>-0.030386515231548131</v>
+        <v>-0.027918660603906215</v>
       </c>
       <c r="Q4" s="0">
-        <v>-0.0034127310557353595</v>
+        <v>0.0017374027697376762</v>
       </c>
       <c r="R4" s="0">
-        <v>-0.005468652224786567</v>
+        <v>-0.00025141192979900975</v>
       </c>
       <c r="S4" s="0">
-        <v>-0.0063006969670956602</v>
+        <v>-0.0010772269062559103</v>
       </c>
       <c r="T4" s="0">
-        <v>0.0024483592493035771</v>
+        <v>0.0025038386294324367</v>
       </c>
       <c r="U4" s="0">
-        <v>0.27184583441420668</v>
+        <v>0.27094958376840617</v>
       </c>
       <c r="V4" s="0">
-        <v>0.27593742151712203</v>
+        <v>0.27534228899403562</v>
       </c>
       <c r="W4" s="0">
-        <v>0.26374256265006835</v>
+        <v>0.27296317070395226</v>
       </c>
       <c r="X4" s="0">
-        <v>0.00072958287138001805</v>
+        <v>0.00085441645726914007</v>
       </c>
       <c r="Y4" s="0">
-        <v>0.098206993134072176</v>
+        <v>0.10118618173432943</v>
       </c>
       <c r="Z4" s="0">
-        <v>0.064333080063640316</v>
+        <v>0.068105006664249221</v>
       </c>
       <c r="AA4" s="0">
-        <v>0.068868983192215114</v>
+        <v>0.072732486800085705</v>
       </c>
       <c r="AB4" s="0">
-        <v>0.010435189398150713</v>
+        <v>0.01322786575041918</v>
       </c>
       <c r="AC4" s="0">
-        <v>0.26627376663436803</v>
+        <v>0.26550769024494908</v>
       </c>
       <c r="AD4" s="0">
-        <v>0.25369238551614354</v>
+        <v>0.25331630498880703</v>
       </c>
       <c r="AE4" s="0">
-        <v>0.2520971877076903</v>
+        <v>0.25184222453224003</v>
       </c>
       <c r="AF4" s="0">
-        <v>0.030265051500254974</v>
+        <v>0.032597087395675725</v>
       </c>
       <c r="AG4" s="0">
-        <v>0.271863597872956</v>
+        <v>0.27094783932089828</v>
       </c>
       <c r="AH4" s="0">
-        <v>0.27189520421507113</v>
+        <v>0.27095063678855352</v>
       </c>
       <c r="AI4" s="0">
-        <v>0.26978819619210004</v>
+        <v>0.26882526646901217</v>
       </c>
       <c r="AJ4" s="0">
-        <v>0.0013019574177650811</v>
+        <v>0.0014342029303310135</v>
       </c>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="5" x14ac:dyDescent="0.3">
@@ -3979,109 +3979,109 @@
         <v>39</v>
       </c>
       <c r="B5" s="0">
-        <v>0.00052805375306565346</v>
+        <v>0.00068216827809869255</v>
       </c>
       <c r="C5" s="0">
-        <v>0.00012599955740686587</v>
+        <v>0</v>
       </c>
       <c r="D5" s="0">
-        <v>0.0039494184072682475</v>
+        <v>0</v>
       </c>
       <c r="E5" s="0">
-        <v>0.0010161699285689415</v>
+        <v>0.0058507314620216628</v>
       </c>
       <c r="F5" s="0">
-        <v>-0.00060688609417410434</v>
+        <v>0.0044330919845435111</v>
       </c>
       <c r="G5" s="0">
-        <v>0.010665362428811569</v>
+        <v>0.015251844668204518</v>
       </c>
       <c r="H5" s="0">
-        <v>-0.00012489294829014949</v>
+        <v>0</v>
       </c>
       <c r="I5" s="0">
-        <v>0.10585608592275894</v>
+        <v>0.11000383142714872</v>
       </c>
       <c r="J5" s="0">
-        <v>0.11421340616896285</v>
+        <v>0.11812718006030193</v>
       </c>
       <c r="K5" s="0">
-        <v>0.031660785088198376</v>
+        <v>0.036348620620985317</v>
       </c>
       <c r="L5" s="0">
-        <v>0.03714128367482887</v>
+        <v>0.041708534038100285</v>
       </c>
       <c r="M5" s="0">
-        <v>0.12021613927738199</v>
+        <v>0.11960985947931886</v>
       </c>
       <c r="N5" s="0">
-        <v>0.02819464583152655</v>
+        <v>0.032864283183984586</v>
       </c>
       <c r="O5" s="0">
-        <v>0.018626820458988363</v>
+        <v>0.023258300919669094</v>
       </c>
       <c r="P5" s="0">
-        <v>-0.0073045784774448015</v>
+        <v>-0.0076895474297222271</v>
       </c>
       <c r="Q5" s="0">
-        <v>1.509485113317332e-05</v>
+        <v>-2.5307750074737803e-06</v>
       </c>
       <c r="R5" s="0">
-        <v>-1.7292642094715359e-05</v>
+        <v>0</v>
       </c>
       <c r="S5" s="0">
-        <v>0.00042789023401756319</v>
+        <v>0</v>
       </c>
       <c r="T5" s="0">
-        <v>0.0022491359225191797</v>
+        <v>0</v>
       </c>
       <c r="U5" s="0">
-        <v>0.037892660144438192</v>
+        <v>0.042437766273161162</v>
       </c>
       <c r="V5" s="0">
-        <v>0.036849670974014891</v>
+        <v>0.041573286681805793</v>
       </c>
       <c r="W5" s="0">
-        <v>0.037438262191840363</v>
+        <v>0.043441494446926722</v>
       </c>
       <c r="X5" s="0">
-        <v>-0.00017683494868029809</v>
+        <v>0</v>
       </c>
       <c r="Y5" s="0">
-        <v>0.0064035215170559316</v>
+        <v>0.0083106348846243173</v>
       </c>
       <c r="Z5" s="0">
-        <v>0.0017062450086223629</v>
+        <v>0.0030542613163875212</v>
       </c>
       <c r="AA5" s="0">
-        <v>0.0097809175299450081</v>
+        <v>0.011008401988855972</v>
       </c>
       <c r="AB5" s="0">
-        <v>0.00058127570009993963</v>
+        <v>0</v>
       </c>
       <c r="AC5" s="0">
-        <v>0.035978334725257556</v>
+        <v>0.040464364161809444</v>
       </c>
       <c r="AD5" s="0">
-        <v>0.01637328166846785</v>
+        <v>0.021215496957842427</v>
       </c>
       <c r="AE5" s="0">
-        <v>0.018076449614993682</v>
+        <v>0.022840522976543942</v>
       </c>
       <c r="AF5" s="0">
-        <v>0.0076934301345981714</v>
+        <v>0</v>
       </c>
       <c r="AG5" s="0">
-        <v>0.036454133819985614</v>
+        <v>0.041042608256070298</v>
       </c>
       <c r="AH5" s="0">
-        <v>0.035345530918572947</v>
+        <v>0.039967080620995146</v>
       </c>
       <c r="AI5" s="0">
-        <v>0.042239793120318246</v>
+        <v>0.046600070639571244</v>
       </c>
       <c r="AJ5" s="0">
-        <v>-0.0001802772491732327</v>
+        <v>-0.00014557166284327595</v>
       </c>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="6" x14ac:dyDescent="0.3">
@@ -4089,109 +4089,109 @@
         <v>40</v>
       </c>
       <c r="B6" s="0">
-        <v>-0.00016075571142501</v>
+        <v>0</v>
       </c>
       <c r="C6" s="0">
-        <v>-6.3972967396792356e-05</v>
+        <v>0</v>
       </c>
       <c r="D6" s="0">
-        <v>0.0017316603723654949</v>
+        <v>0</v>
       </c>
       <c r="E6" s="0">
-        <v>0.00033821743626009319</v>
+        <v>0.00043337078231809342</v>
       </c>
       <c r="F6" s="0">
-        <v>7.3451668751924658e-05</v>
+        <v>0.00013177336593910206</v>
       </c>
       <c r="G6" s="0">
-        <v>0.0012547366890375432</v>
+        <v>0.0016131448795317865</v>
       </c>
       <c r="H6" s="0">
-        <v>-0.00020870934182878827</v>
+        <v>0</v>
       </c>
       <c r="I6" s="0">
-        <v>-0.0015325022117363227</v>
+        <v>0.0019424251121970422</v>
       </c>
       <c r="J6" s="0">
-        <v>0.00014685004927314797</v>
+        <v>0.0038119760558265755</v>
       </c>
       <c r="K6" s="0">
-        <v>0.0011206219225265283</v>
+        <v>0.002148455801638206</v>
       </c>
       <c r="L6" s="0">
-        <v>0.0021055985679702886</v>
+        <v>0.0032645716799449939</v>
       </c>
       <c r="M6" s="0">
-        <v>0.099998902406357143</v>
+        <v>0.099574907658122089</v>
       </c>
       <c r="N6" s="0">
-        <v>0.00065851503377632509</v>
+        <v>0.0015961185420488131</v>
       </c>
       <c r="O6" s="0">
-        <v>0.00083582338078565992</v>
+        <v>0.0014630976972215693</v>
       </c>
       <c r="P6" s="0">
-        <v>-0.00048564067025207332</v>
+        <v>-0.0007022233179339516</v>
       </c>
       <c r="Q6" s="0">
-        <v>-4.8198280337950839e-05</v>
+        <v>0</v>
       </c>
       <c r="R6" s="0">
-        <v>3.4087517024101037e-05</v>
+        <v>0</v>
       </c>
       <c r="S6" s="0">
-        <v>0.0001727894218026554</v>
+        <v>0</v>
       </c>
       <c r="T6" s="0">
-        <v>0.00045698169589914486</v>
+        <v>0</v>
       </c>
       <c r="U6" s="0">
-        <v>0.001012251999007904</v>
+        <v>0.0022394264095400504</v>
       </c>
       <c r="V6" s="0">
-        <v>0.00052978040597324307</v>
+        <v>0.0017487191679863704</v>
       </c>
       <c r="W6" s="0">
-        <v>0.001617818216260935</v>
+        <v>0.0029109145819307199</v>
       </c>
       <c r="X6" s="0">
-        <v>0.00011669510767868108</v>
+        <v>0</v>
       </c>
       <c r="Y6" s="0">
-        <v>-0.00020341233949728086</v>
+        <v>3.7771285610959906e-05</v>
       </c>
       <c r="Z6" s="0">
-        <v>-4.9947279922486416e-05</v>
+        <v>0</v>
       </c>
       <c r="AA6" s="0">
-        <v>0.0030382559056352149</v>
+        <v>0</v>
       </c>
       <c r="AB6" s="0">
-        <v>0.00023625509488027277</v>
+        <v>0</v>
       </c>
       <c r="AC6" s="0">
-        <v>0.0015197193433635731</v>
+        <v>0.0026639550823640704</v>
       </c>
       <c r="AD6" s="0">
-        <v>-0.00072579026243930784</v>
+        <v>-0.00010043914974234257</v>
       </c>
       <c r="AE6" s="0">
-        <v>8.423837661560337e-05</v>
+        <v>0.00072796499883543591</v>
       </c>
       <c r="AF6" s="0">
-        <v>0.0037958676330538013</v>
+        <v>0</v>
       </c>
       <c r="AG6" s="0">
-        <v>0.00210171360872994</v>
+        <v>0.0032381573102581527</v>
       </c>
       <c r="AH6" s="0">
-        <v>0.00042113044709646172</v>
+        <v>0.0015938026742861608</v>
       </c>
       <c r="AI6" s="0">
-        <v>0.0039482058094148708</v>
+        <v>0.0051859915675512664</v>
       </c>
       <c r="AJ6" s="0">
-        <v>0.0010094489329634171</v>
+        <v>0.00096178589098464072</v>
       </c>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="7" x14ac:dyDescent="0.3">
@@ -4199,109 +4199,109 @@
         <v>41</v>
       </c>
       <c r="B7" s="0">
-        <v>-3.5732146242003231e-05</v>
+        <v>0</v>
       </c>
       <c r="C7" s="0">
-        <v>-4.9079845390417008e-05</v>
+        <v>0</v>
       </c>
       <c r="D7" s="0">
-        <v>-1.287290088547776e-05</v>
+        <v>0</v>
       </c>
       <c r="E7" s="0">
-        <v>-1.4042713922751952e-05</v>
+        <v>2.342511634470986e-06</v>
       </c>
       <c r="F7" s="0">
-        <v>-6.6334862882646295e-05</v>
+        <v>0</v>
       </c>
       <c r="G7" s="0">
-        <v>0.00061254823532257781</v>
+        <v>0</v>
       </c>
       <c r="H7" s="0">
-        <v>6.1015026927038125e-05</v>
+        <v>0</v>
       </c>
       <c r="I7" s="0">
-        <v>-7.7827857097951581e-06</v>
+        <v>1.9150241981996001e-06</v>
       </c>
       <c r="J7" s="0">
-        <v>0.00024179975378953969</v>
+        <v>0.00031294916816916086</v>
       </c>
       <c r="K7" s="0">
-        <v>-2.4198797046489283e-05</v>
+        <v>4.5364598150730737e-05</v>
       </c>
       <c r="L7" s="0">
-        <v>0.00052317848042247319</v>
+        <v>0.00060842470443880448</v>
       </c>
       <c r="M7" s="0">
-        <v>0.021901188591579773</v>
+        <v>0.024934660376540248</v>
       </c>
       <c r="N7" s="0">
-        <v>0.00026103734360074854</v>
+        <v>0.00029438600189001207</v>
       </c>
       <c r="O7" s="0">
-        <v>0.0047738202515144202</v>
+        <v>0.0045716741802845091</v>
       </c>
       <c r="P7" s="0">
-        <v>0.039991419966531418</v>
+        <v>0.037872272423713618</v>
       </c>
       <c r="Q7" s="0">
-        <v>8.9310206761374033e-07</v>
+        <v>0</v>
       </c>
       <c r="R7" s="0">
-        <v>-1.493046043739367e-05</v>
+        <v>0</v>
       </c>
       <c r="S7" s="0">
-        <v>0.00011045261380420053</v>
+        <v>0</v>
       </c>
       <c r="T7" s="0">
-        <v>0.0002593625850491187</v>
+        <v>0</v>
       </c>
       <c r="U7" s="0">
-        <v>-3.042142424363731e-05</v>
+        <v>3.918682441568514e-05</v>
       </c>
       <c r="V7" s="0">
-        <v>0.00014166165971870876</v>
+        <v>0.00018207529096716553</v>
       </c>
       <c r="W7" s="0">
-        <v>0.00044673767209908835</v>
+        <v>0.0005358011725403643</v>
       </c>
       <c r="X7" s="0">
-        <v>0.00035243835753705839</v>
+        <v>0</v>
       </c>
       <c r="Y7" s="0">
-        <v>-9.7522023214081813e-05</v>
+        <v>0</v>
       </c>
       <c r="Z7" s="0">
-        <v>2.1963824464213293e-05</v>
+        <v>0</v>
       </c>
       <c r="AA7" s="0">
-        <v>0.00048413284072195052</v>
+        <v>0</v>
       </c>
       <c r="AB7" s="0">
-        <v>7.4498167225556635e-05</v>
+        <v>0</v>
       </c>
       <c r="AC7" s="0">
-        <v>-0.00025185700499696126</v>
+        <v>-0.00015114718002689286</v>
       </c>
       <c r="AD7" s="0">
-        <v>-0.00040211967999749981</v>
+        <v>0</v>
       </c>
       <c r="AE7" s="0">
-        <v>8.8252084609863245e-05</v>
+        <v>0</v>
       </c>
       <c r="AF7" s="0">
-        <v>0.001702483642803732</v>
+        <v>0</v>
       </c>
       <c r="AG7" s="0">
-        <v>-0.0002010231192506947</v>
+        <v>-7.877509566077622e-05</v>
       </c>
       <c r="AH7" s="0">
-        <v>-1.1457644247565906e-05</v>
+        <v>3.1224606319193858e-05</v>
       </c>
       <c r="AI7" s="0">
-        <v>-0.00089216648542510572</v>
+        <v>-0.00065418572882302033</v>
       </c>
       <c r="AJ7" s="0">
-        <v>0.0038459620202633388</v>
+        <v>0.0036858307626799957</v>
       </c>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="8" x14ac:dyDescent="0.3">
@@ -4309,109 +4309,109 @@
         <v>42</v>
       </c>
       <c r="B8" s="0">
-        <v>-9.4385619584231514e-06</v>
+        <v>0</v>
       </c>
       <c r="C8" s="0">
-        <v>-8.1904836459470082e-05</v>
+        <v>0</v>
       </c>
       <c r="D8" s="0">
-        <v>-9.1449298928553553e-05</v>
+        <v>0</v>
       </c>
       <c r="E8" s="0">
-        <v>6.9665581946203831e-06</v>
+        <v>0</v>
       </c>
       <c r="F8" s="0">
-        <v>2.5280956132889408e-06</v>
+        <v>0</v>
       </c>
       <c r="G8" s="0">
-        <v>1.7039575370873749e-05</v>
+        <v>0</v>
       </c>
       <c r="H8" s="0">
-        <v>-0.00011789937978727867</v>
+        <v>0</v>
       </c>
       <c r="I8" s="0">
-        <v>-2.120084121365674e-05</v>
+        <v>0</v>
       </c>
       <c r="J8" s="0">
-        <v>0.00011131881878272155</v>
+        <v>0</v>
       </c>
       <c r="K8" s="0">
-        <v>-1.6603913580196783e-06</v>
+        <v>0</v>
       </c>
       <c r="L8" s="0">
-        <v>0.00011745953012289524</v>
+        <v>0</v>
       </c>
       <c r="M8" s="0">
-        <v>0.0019153268833527002</v>
+        <v>0.0030170618047431334</v>
       </c>
       <c r="N8" s="0">
-        <v>7.1370494397417431e-05</v>
+        <v>8.1217055264830139e-05</v>
       </c>
       <c r="O8" s="0">
-        <v>0.0029422194064961144</v>
+        <v>0.0030014887445645416</v>
       </c>
       <c r="P8" s="0">
-        <v>-0.010299448713858064</v>
+        <v>-0.0076287849839246592</v>
       </c>
       <c r="Q8" s="0">
-        <v>3.3510128589762457e-06</v>
+        <v>0</v>
       </c>
       <c r="R8" s="0">
-        <v>-0.00064105978392175003</v>
+        <v>0</v>
       </c>
       <c r="S8" s="0">
-        <v>-0.00018981034682782316</v>
+        <v>0</v>
       </c>
       <c r="T8" s="0">
-        <v>-0.00019169111644607863</v>
+        <v>0</v>
       </c>
       <c r="U8" s="0">
-        <v>0.00014556242879655657</v>
+        <v>0.00013650713971400248</v>
       </c>
       <c r="V8" s="0">
-        <v>0.00026258426332466937</v>
+        <v>0.00025477154184724827</v>
       </c>
       <c r="W8" s="0">
-        <v>0.00011539520457358282</v>
+        <v>0.00013821521691172056</v>
       </c>
       <c r="X8" s="0">
-        <v>-0.00013519732000180778</v>
+        <v>0</v>
       </c>
       <c r="Y8" s="0">
-        <v>3.4161541190809391e-05</v>
+        <v>0</v>
       </c>
       <c r="Z8" s="0">
-        <v>1.4002820515896796e-05</v>
+        <v>0</v>
       </c>
       <c r="AA8" s="0">
-        <v>9.8275737385120808e-05</v>
+        <v>0</v>
       </c>
       <c r="AB8" s="0">
-        <v>-0.00019837465309148873</v>
+        <v>0</v>
       </c>
       <c r="AC8" s="0">
-        <v>-2.5637914980053196e-07</v>
+        <v>0</v>
       </c>
       <c r="AD8" s="0">
-        <v>0.00013130238440719997</v>
+        <v>0</v>
       </c>
       <c r="AE8" s="0">
-        <v>2.918796018245749e-05</v>
+        <v>0</v>
       </c>
       <c r="AF8" s="0">
-        <v>-0.0011582252492819889</v>
+        <v>0</v>
       </c>
       <c r="AG8" s="0">
-        <v>-0.00010474756250865571</v>
+        <v>-0.00010563688002585807</v>
       </c>
       <c r="AH8" s="0">
-        <v>0.00013497457004564795</v>
+        <v>0.00012684694460036587</v>
       </c>
       <c r="AI8" s="0">
-        <v>0.00027537556616302934</v>
+        <v>0.00021777961499927433</v>
       </c>
       <c r="AJ8" s="0">
-        <v>-0.0011445059700407939</v>
+        <v>-0.00087687748391811042</v>
       </c>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="9" x14ac:dyDescent="0.3">
@@ -4419,109 +4419,109 @@
         <v>43</v>
       </c>
       <c r="B9" s="0">
-        <v>-4.4453312453702832e-06</v>
+        <v>0</v>
       </c>
       <c r="C9" s="0">
-        <v>1.6861874646616096e-05</v>
+        <v>0</v>
       </c>
       <c r="D9" s="0">
-        <v>7.1136800813966234e-06</v>
+        <v>0</v>
       </c>
       <c r="E9" s="0">
-        <v>2.8182668074772046e-06</v>
+        <v>0</v>
       </c>
       <c r="F9" s="0">
-        <v>5.6389751625054068e-06</v>
+        <v>0</v>
       </c>
       <c r="G9" s="0">
-        <v>6.7898986855666581e-05</v>
+        <v>0</v>
       </c>
       <c r="H9" s="0">
-        <v>1.6588765694487467e-05</v>
+        <v>0</v>
       </c>
       <c r="I9" s="0">
-        <v>0.00010706258388628536</v>
+        <v>0</v>
       </c>
       <c r="J9" s="0">
-        <v>0.00022633971622000747</v>
+        <v>0</v>
       </c>
       <c r="K9" s="0">
-        <v>-7.2616910488713325e-05</v>
+        <v>0</v>
       </c>
       <c r="L9" s="0">
-        <v>0.00037983051003391744</v>
+        <v>0</v>
       </c>
       <c r="M9" s="0">
-        <v>0.00014529437190601087</v>
+        <v>0.00028804508209658258</v>
       </c>
       <c r="N9" s="0">
-        <v>0.00020930049646203779</v>
+        <v>0.00019885966058365409</v>
       </c>
       <c r="O9" s="0">
-        <v>0.00054074510192708377</v>
+        <v>0.00068639639596647904</v>
       </c>
       <c r="P9" s="0">
-        <v>-0.0013455534132147927</v>
+        <v>-0.0018027733573175563</v>
       </c>
       <c r="Q9" s="0">
-        <v>-0.000103106646607807</v>
+        <v>0</v>
       </c>
       <c r="R9" s="0">
-        <v>0.0001320874378439638</v>
+        <v>0</v>
       </c>
       <c r="S9" s="0">
-        <v>2.5207380868672231e-05</v>
+        <v>0</v>
       </c>
       <c r="T9" s="0">
-        <v>6.1972960343863713e-06</v>
+        <v>0</v>
       </c>
       <c r="U9" s="0">
-        <v>5.3192490809336026e-05</v>
+        <v>5.8080332526937084e-05</v>
       </c>
       <c r="V9" s="0">
-        <v>0.00021678169825607466</v>
+        <v>0.00021743782071258311</v>
       </c>
       <c r="W9" s="0">
-        <v>6.3774107132460255e-05</v>
+        <v>6.9452996872741173e-05</v>
       </c>
       <c r="X9" s="0">
-        <v>-4.4668965562614826e-06</v>
+        <v>0</v>
       </c>
       <c r="Y9" s="0">
-        <v>1.5053787040674789e-05</v>
+        <v>0</v>
       </c>
       <c r="Z9" s="0">
-        <v>-0.00021957221381372794</v>
+        <v>0</v>
       </c>
       <c r="AA9" s="0">
-        <v>-0.00020629443832361464</v>
+        <v>0</v>
       </c>
       <c r="AB9" s="0">
-        <v>2.5911546276854122e-05</v>
+        <v>0</v>
       </c>
       <c r="AC9" s="0">
-        <v>2.7810997700678623e-06</v>
+        <v>0</v>
       </c>
       <c r="AD9" s="0">
-        <v>0.0001327806665839681</v>
+        <v>0</v>
       </c>
       <c r="AE9" s="0">
-        <v>7.4115681790530355e-05</v>
+        <v>0</v>
       </c>
       <c r="AF9" s="0">
-        <v>2.276373356000756e-05</v>
+        <v>0</v>
       </c>
       <c r="AG9" s="0">
-        <v>0.00021002326449450233</v>
+        <v>0.00018821352161949611</v>
       </c>
       <c r="AH9" s="0">
-        <v>-5.3995695037655421e-05</v>
+        <v>-4.1954228341825e-05</v>
       </c>
       <c r="AI9" s="0">
-        <v>-0.0001192037588823624</v>
+        <v>-9.5333899750078442e-05</v>
       </c>
       <c r="AJ9" s="0">
-        <v>-0.00011203259975394006</v>
+        <v>-0.00016650776777979239</v>
       </c>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="10" x14ac:dyDescent="0.3">
@@ -4529,109 +4529,109 @@
         <v>44</v>
       </c>
       <c r="B10" s="0">
-        <v>1.9973377064037295e-06</v>
+        <v>0</v>
       </c>
       <c r="C10" s="0">
-        <v>4.1197578746965899e-06</v>
+        <v>0</v>
       </c>
       <c r="D10" s="0">
-        <v>2.6170769574364279e-06</v>
+        <v>0</v>
       </c>
       <c r="E10" s="0">
-        <v>8.5775519279958647e-06</v>
+        <v>0</v>
       </c>
       <c r="F10" s="0">
-        <v>-4.9750523982698125e-06</v>
+        <v>0</v>
       </c>
       <c r="G10" s="0">
-        <v>-1.5111920446591826e-05</v>
+        <v>0</v>
       </c>
       <c r="H10" s="0">
-        <v>6.3481172008479782e-06</v>
+        <v>0</v>
       </c>
       <c r="I10" s="0">
-        <v>8.0737384488876294e-05</v>
+        <v>0</v>
       </c>
       <c r="J10" s="0">
-        <v>2.4955556032708789e-05</v>
+        <v>0</v>
       </c>
       <c r="K10" s="0">
-        <v>7.9907901075621737e-06</v>
+        <v>0</v>
       </c>
       <c r="L10" s="0">
-        <v>6.9360507863203556e-07</v>
+        <v>0</v>
       </c>
       <c r="M10" s="0">
-        <v>4.4578886049347221e-05</v>
+        <v>5.624728211992141e-05</v>
       </c>
       <c r="N10" s="0">
-        <v>-7.3793310879696324e-05</v>
+        <v>-5.299686389354789e-05</v>
       </c>
       <c r="O10" s="0">
-        <v>-0.00024428771573495361</v>
+        <v>-0.00017975323356029621</v>
       </c>
       <c r="P10" s="0">
-        <v>0.0007106709324315784</v>
+        <v>0.00053700593444923263</v>
       </c>
       <c r="Q10" s="0">
-        <v>2.4453221634122731e-05</v>
+        <v>0</v>
       </c>
       <c r="R10" s="0">
-        <v>4.7556916840857917e-05</v>
+        <v>0</v>
       </c>
       <c r="S10" s="0">
-        <v>9.3936351991595061e-06</v>
+        <v>0</v>
       </c>
       <c r="T10" s="0">
-        <v>1.1114718639652259e-05</v>
+        <v>0</v>
       </c>
       <c r="U10" s="0">
-        <v>-6.328129853664444e-05</v>
+        <v>-5.4043873203896767e-05</v>
       </c>
       <c r="V10" s="0">
-        <v>-0.00011530861708267283</v>
+        <v>-9.0278557542426891e-05</v>
       </c>
       <c r="W10" s="0">
-        <v>-2.3994681706613998e-05</v>
+        <v>-1.7976439590579821e-05</v>
       </c>
       <c r="X10" s="0">
-        <v>8.3842325825617624e-06</v>
+        <v>0</v>
       </c>
       <c r="Y10" s="0">
-        <v>-5.3046848932473059e-05</v>
+        <v>0</v>
       </c>
       <c r="Z10" s="0">
-        <v>4.6382912521111378e-05</v>
+        <v>0</v>
       </c>
       <c r="AA10" s="0">
-        <v>2.0590615097027641e-05</v>
+        <v>0</v>
       </c>
       <c r="AB10" s="0">
-        <v>1.0355926013356476e-05</v>
+        <v>0</v>
       </c>
       <c r="AC10" s="0">
-        <v>1.3652595076900865e-06</v>
+        <v>0</v>
       </c>
       <c r="AD10" s="0">
-        <v>-0.00013895033427265842</v>
+        <v>0</v>
       </c>
       <c r="AE10" s="0">
-        <v>-4.3691147179641418e-05</v>
+        <v>0</v>
       </c>
       <c r="AF10" s="0">
-        <v>6.7263999375576336e-05</v>
+        <v>0</v>
       </c>
       <c r="AG10" s="0">
-        <v>0.00033151986568154929</v>
+        <v>0.00031852860693209404</v>
       </c>
       <c r="AH10" s="0">
-        <v>0.00035075628181065671</v>
+        <v>0.00031836406509065386</v>
       </c>
       <c r="AI10" s="0">
-        <v>0.0001214845128028819</v>
+        <v>0.00010377225198516693</v>
       </c>
       <c r="AJ10" s="0">
-        <v>7.596884679697354e-05</v>
+        <v>5.9498736877011617e-05</v>
       </c>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="11" x14ac:dyDescent="0.3">
@@ -4639,109 +4639,109 @@
         <v>45</v>
       </c>
       <c r="B11" s="0">
-        <v>1.78049882872363e-07</v>
+        <v>0</v>
       </c>
       <c r="C11" s="0">
-        <v>-1.2567572677362206e-06</v>
+        <v>0</v>
       </c>
       <c r="D11" s="0">
-        <v>-3.68329209029917e-07</v>
+        <v>0</v>
       </c>
       <c r="E11" s="0">
-        <v>-3.0441849607689764e-06</v>
+        <v>0</v>
       </c>
       <c r="F11" s="0">
-        <v>5.5453262378129961e-07</v>
+        <v>0</v>
       </c>
       <c r="G11" s="0">
-        <v>-7.8881618427788294e-07</v>
+        <v>0</v>
       </c>
       <c r="H11" s="0">
-        <v>-1.4700892503820111e-06</v>
+        <v>0</v>
       </c>
       <c r="I11" s="0">
-        <v>-3.2316490209715546e-05</v>
+        <v>0</v>
       </c>
       <c r="J11" s="0">
-        <v>-1.5755797345624023e-05</v>
+        <v>0</v>
       </c>
       <c r="K11" s="0">
-        <v>3.9316657560609684e-06</v>
+        <v>0</v>
       </c>
       <c r="L11" s="0">
-        <v>-1.8812339753459147e-05</v>
+        <v>0</v>
       </c>
       <c r="M11" s="0">
-        <v>-0.00015124400901959971</v>
+        <v>-0.00013321099939980722</v>
       </c>
       <c r="N11" s="0">
-        <v>-4.6287878829734936e-06</v>
+        <v>-9.3703521248322358e-06</v>
       </c>
       <c r="O11" s="0">
-        <v>2.1660059892646784e-06</v>
+        <v>-1.5419418405683865e-05</v>
       </c>
       <c r="P11" s="0">
-        <v>1.141161157371172e-05</v>
+        <v>6.1547340460401867e-05</v>
       </c>
       <c r="Q11" s="0">
-        <v>7.1510931997828029e-06</v>
+        <v>0</v>
       </c>
       <c r="R11" s="0">
-        <v>-1.4843481848582766e-05</v>
+        <v>0</v>
       </c>
       <c r="S11" s="0">
-        <v>-2.1642692892490968e-06</v>
+        <v>0</v>
       </c>
       <c r="T11" s="0">
-        <v>-1.2031736332005013e-06</v>
+        <v>0</v>
       </c>
       <c r="U11" s="0">
-        <v>7.0172818766740193e-06</v>
+        <v>1.5671314850771918e-06</v>
       </c>
       <c r="V11" s="0">
-        <v>5.8068058210752306e-05</v>
+        <v>0</v>
       </c>
       <c r="W11" s="0">
-        <v>6.2922392599244374e-07</v>
+        <v>0</v>
       </c>
       <c r="X11" s="0">
-        <v>-4.7952403628878304e-07</v>
+        <v>0</v>
       </c>
       <c r="Y11" s="0">
-        <v>1.0711047736321516e-05</v>
+        <v>0</v>
       </c>
       <c r="Z11" s="0">
-        <v>1.5958479159339751e-05</v>
+        <v>0</v>
       </c>
       <c r="AA11" s="0">
-        <v>1.1030682896539152e-05</v>
+        <v>0</v>
       </c>
       <c r="AB11" s="0">
-        <v>-2.2689308588929069e-06</v>
+        <v>0</v>
       </c>
       <c r="AC11" s="0">
-        <v>-1.9715914725619875e-05</v>
+        <v>0</v>
       </c>
       <c r="AD11" s="0">
-        <v>1.6426483481839997e-05</v>
+        <v>0</v>
       </c>
       <c r="AE11" s="0">
-        <v>2.1629423715891006e-06</v>
+        <v>0</v>
       </c>
       <c r="AF11" s="0">
-        <v>-6.4067292605194953e-06</v>
+        <v>0</v>
       </c>
       <c r="AG11" s="0">
-        <v>-7.8356647401556321e-05</v>
+        <v>-4.4470409012488164e-05</v>
       </c>
       <c r="AH11" s="0">
-        <v>-0.00015724566758819941</v>
+        <v>-0.00011533040265950892</v>
       </c>
       <c r="AI11" s="0">
-        <v>-3.356394581269464e-05</v>
+        <v>-2.1262579549543204e-05</v>
       </c>
       <c r="AJ11" s="0">
-        <v>-3.6416297842126559e-07</v>
+        <v>5.2327806913993952e-06</v>
       </c>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="12" x14ac:dyDescent="0.3">
@@ -4749,109 +4749,109 @@
         <v>46</v>
       </c>
       <c r="B12" s="0">
-        <v>-1.3232117381922174e-07</v>
+        <v>0</v>
       </c>
       <c r="C12" s="0">
-        <v>-1.2447928067376365e-07</v>
+        <v>0</v>
       </c>
       <c r="D12" s="0">
-        <v>-6.8969225782394866e-08</v>
+        <v>0</v>
       </c>
       <c r="E12" s="0">
-        <v>-1.7923668733726778e-07</v>
+        <v>0</v>
       </c>
       <c r="F12" s="0">
-        <v>2.5393593771133106e-07</v>
+        <v>0</v>
       </c>
       <c r="G12" s="0">
-        <v>5.1290969379445634e-07</v>
+        <v>0</v>
       </c>
       <c r="H12" s="0">
-        <v>-2.1635347850717547e-07</v>
+        <v>0</v>
       </c>
       <c r="I12" s="0">
-        <v>-1.4659135765697448e-06</v>
+        <v>0</v>
       </c>
       <c r="J12" s="0">
-        <v>4.802442424381378e-07</v>
+        <v>0</v>
       </c>
       <c r="K12" s="0">
-        <v>-6.7194908674054952e-07</v>
+        <v>0</v>
       </c>
       <c r="L12" s="0">
-        <v>1.4169780552310186e-06</v>
+        <v>0</v>
       </c>
       <c r="M12" s="0">
-        <v>1.6595540958720123e-05</v>
+        <v>1.8679585012699865e-06</v>
       </c>
       <c r="N12" s="0">
-        <v>4.712349218525491e-06</v>
+        <v>3.568129411490642e-06</v>
       </c>
       <c r="O12" s="0">
-        <v>7.7008752548636802e-06</v>
+        <v>6.2371904436704312e-06</v>
       </c>
       <c r="P12" s="0">
-        <v>-3.4461907779678922e-05</v>
+        <v>-2.7405645040689532e-05</v>
       </c>
       <c r="Q12" s="0">
-        <v>-2.6903891246520384e-06</v>
+        <v>0</v>
       </c>
       <c r="R12" s="0">
-        <v>-1.9249615473834494e-06</v>
+        <v>0</v>
       </c>
       <c r="S12" s="0">
-        <v>-3.0701714547541235e-07</v>
+        <v>0</v>
       </c>
       <c r="T12" s="0">
-        <v>-4.5691822841484934e-07</v>
+        <v>0</v>
       </c>
       <c r="U12" s="0">
-        <v>3.1307704014564384e-06</v>
+        <v>0</v>
       </c>
       <c r="V12" s="0">
-        <v>0.00063451536266093491</v>
+        <v>0</v>
       </c>
       <c r="W12" s="0">
-        <v>0.0041572121305707074</v>
+        <v>0</v>
       </c>
       <c r="X12" s="0">
-        <v>-3.6760063248461666e-07</v>
+        <v>0</v>
       </c>
       <c r="Y12" s="0">
-        <v>3.7800274936924201e-06</v>
+        <v>0</v>
       </c>
       <c r="Z12" s="0">
-        <v>-5.2533568624847366e-06</v>
+        <v>0</v>
       </c>
       <c r="AA12" s="0">
-        <v>-1.9620763883260434e-06</v>
+        <v>0</v>
       </c>
       <c r="AB12" s="0">
-        <v>-3.5542952022876354e-07</v>
+        <v>0</v>
       </c>
       <c r="AC12" s="0">
-        <v>4.9398100515930906e-06</v>
+        <v>0</v>
       </c>
       <c r="AD12" s="0">
-        <v>1.0440909893057101e-05</v>
+        <v>0</v>
       </c>
       <c r="AE12" s="0">
-        <v>2.4164098240741496e-06</v>
+        <v>0</v>
       </c>
       <c r="AF12" s="0">
-        <v>-2.8060514209967846e-06</v>
+        <v>0</v>
       </c>
       <c r="AG12" s="0">
-        <v>-4.1347517497505171e-05</v>
+        <v>-4.2706223242193714e-05</v>
       </c>
       <c r="AH12" s="0">
-        <v>0.0006782684843299661</v>
+        <v>0.00059662657985979858</v>
       </c>
       <c r="AI12" s="0">
-        <v>-1.6423979362991522e-06</v>
+        <v>-3.9603664497481994e-06</v>
       </c>
       <c r="AJ12" s="0">
-        <v>-3.5822951528805468e-06</v>
+        <v>-2.9738654872398868e-06</v>
       </c>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="13" x14ac:dyDescent="0.3">
@@ -4859,109 +4859,109 @@
         <v>47</v>
       </c>
       <c r="B13" s="0">
-        <v>-7.6032390215332838e-10</v>
+        <v>0</v>
       </c>
       <c r="C13" s="0">
-        <v>6.7127266215925243e-08</v>
+        <v>0</v>
       </c>
       <c r="D13" s="0">
-        <v>1.5832567352865857e-08</v>
+        <v>0</v>
       </c>
       <c r="E13" s="0">
-        <v>1.9581951841963091e-07</v>
+        <v>0</v>
       </c>
       <c r="F13" s="0">
-        <v>-5.3495967007478637e-08</v>
+        <v>0</v>
       </c>
       <c r="G13" s="0">
-        <v>1.5768215486378052e-09</v>
+        <v>0</v>
       </c>
       <c r="H13" s="0">
-        <v>8.403987314058352e-08</v>
+        <v>0</v>
       </c>
       <c r="I13" s="0">
-        <v>1.9545393194213477e-06</v>
+        <v>0</v>
       </c>
       <c r="J13" s="0">
-        <v>4.7663991669359486e-07</v>
+        <v>0</v>
       </c>
       <c r="K13" s="0">
-        <v>-1.5255941845778821e-07</v>
+        <v>0</v>
       </c>
       <c r="L13" s="0">
-        <v>5.3220916732407763e-07</v>
+        <v>0</v>
       </c>
       <c r="M13" s="0">
-        <v>8.4260442209611285e-06</v>
+        <v>8.3794449953488146e-06</v>
       </c>
       <c r="N13" s="0">
-        <v>-1.3831499666882621e-07</v>
+        <v>2.9885202997490841e-07</v>
       </c>
       <c r="O13" s="0">
-        <v>-4.4993500456334965e-07</v>
+        <v>0</v>
       </c>
       <c r="P13" s="0">
-        <v>1.7994952665332306e-06</v>
+        <v>-1.5672052676757694e-06</v>
       </c>
       <c r="Q13" s="0">
-        <v>-2.4308991763546043e-07</v>
+        <v>0</v>
       </c>
       <c r="R13" s="0">
-        <v>1.0393210573671102e-06</v>
+        <v>0</v>
       </c>
       <c r="S13" s="0">
-        <v>1.2150398451077749e-07</v>
+        <v>0</v>
       </c>
       <c r="T13" s="0">
-        <v>8.535583533085456e-08</v>
+        <v>0</v>
       </c>
       <c r="U13" s="0">
-        <v>-6.4679561951895643e-07</v>
+        <v>0</v>
       </c>
       <c r="V13" s="0">
-        <v>0.0012365955045413543</v>
+        <v>0</v>
       </c>
       <c r="W13" s="0">
-        <v>0.042147713210118398</v>
+        <v>0</v>
       </c>
       <c r="X13" s="0">
-        <v>4.7196608101326664e-08</v>
+        <v>0</v>
       </c>
       <c r="Y13" s="0">
-        <v>-1.2554670212045938e-06</v>
+        <v>0</v>
       </c>
       <c r="Z13" s="0">
-        <v>-6.1243242038518413e-07</v>
+        <v>0</v>
       </c>
       <c r="AA13" s="0">
-        <v>-4.065518569717251e-07</v>
+        <v>0</v>
       </c>
       <c r="AB13" s="0">
-        <v>1.2964768973244811e-07</v>
+        <v>0</v>
       </c>
       <c r="AC13" s="0">
-        <v>1.3083472205587279e-06</v>
+        <v>0</v>
       </c>
       <c r="AD13" s="0">
-        <v>-2.4272104517171804e-06</v>
+        <v>0</v>
       </c>
       <c r="AE13" s="0">
-        <v>-3.293074408004814e-07</v>
+        <v>0</v>
       </c>
       <c r="AF13" s="0">
-        <v>4.763860818983152e-07</v>
+        <v>0</v>
       </c>
       <c r="AG13" s="0">
-        <v>1.3106506808344474e-05</v>
+        <v>7.3496636224724552e-06</v>
       </c>
       <c r="AH13" s="0">
-        <v>0.0012687166243957747</v>
+        <v>0.0011915314114955577</v>
       </c>
       <c r="AI13" s="0">
-        <v>1.9851358356190967e-06</v>
+        <v>1.4649049070942717e-06</v>
       </c>
       <c r="AJ13" s="0">
-        <v>2.5654519171364429e-07</v>
+        <v>-1.0807582852940547e-07</v>
       </c>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="14" x14ac:dyDescent="0.3">
@@ -4969,109 +4969,109 @@
         <v>48</v>
       </c>
       <c r="B14" s="0">
-        <v>6.4367662230847066e-09</v>
+        <v>0</v>
       </c>
       <c r="C14" s="0">
-        <v>1.4933583779509763e-09</v>
+        <v>0</v>
       </c>
       <c r="D14" s="0">
-        <v>1.5045484575854084e-09</v>
+        <v>0</v>
       </c>
       <c r="E14" s="0">
-        <v>-6.7938260318921903e-09</v>
+        <v>0</v>
       </c>
       <c r="F14" s="0">
-        <v>-8.5428009795012785e-09</v>
+        <v>0</v>
       </c>
       <c r="G14" s="0">
-        <v>-1.728656643343365e-08</v>
+        <v>0</v>
       </c>
       <c r="H14" s="0">
-        <v>4.3910825262682636e-09</v>
+        <v>0</v>
       </c>
       <c r="I14" s="0">
-        <v>-7.594250479321894e-08</v>
+        <v>0</v>
       </c>
       <c r="J14" s="0">
-        <v>-3.9213888016850278e-08</v>
+        <v>0</v>
       </c>
       <c r="K14" s="0">
-        <v>3.9934368398438498e-08</v>
+        <v>0</v>
       </c>
       <c r="L14" s="0">
-        <v>-7.3406472395199812e-08</v>
+        <v>0</v>
       </c>
       <c r="M14" s="0">
-        <v>-1.5517835898542677e-06</v>
+        <v>-4.1650647464339626e-07</v>
       </c>
       <c r="N14" s="0">
-        <v>-2.152538040310624e-07</v>
+        <v>-1.7813052365919255e-07</v>
       </c>
       <c r="O14" s="0">
-        <v>-2.3534676442950366e-07</v>
+        <v>0</v>
       </c>
       <c r="P14" s="0">
-        <v>1.3781068110583784e-06</v>
+        <v>1.209327321325348e-06</v>
       </c>
       <c r="Q14" s="0">
-        <v>1.8313361176561915e-07</v>
+        <v>0</v>
       </c>
       <c r="R14" s="0">
-        <v>3.2511936881134308e-08</v>
+        <v>0</v>
       </c>
       <c r="S14" s="0">
-        <v>5.8367145111885306e-09</v>
+        <v>0</v>
       </c>
       <c r="T14" s="0">
-        <v>1.4734468477218128e-08</v>
+        <v>0</v>
       </c>
       <c r="U14" s="0">
-        <v>6.0219311556636718e-05</v>
+        <v>0</v>
       </c>
       <c r="V14" s="0">
-        <v>-0.00041799619165363623</v>
+        <v>0</v>
       </c>
       <c r="W14" s="0">
-        <v>-0.0090511793584562659</v>
+        <v>0</v>
       </c>
       <c r="X14" s="0">
-        <v>1.2999589181624717e-08</v>
+        <v>0</v>
       </c>
       <c r="Y14" s="0">
-        <v>-1.3966002005270974e-07</v>
+        <v>0</v>
       </c>
       <c r="Z14" s="0">
-        <v>3.6575204459682111e-07</v>
+        <v>0</v>
       </c>
       <c r="AA14" s="0">
-        <v>1.1716607133566783e-07</v>
+        <v>0</v>
       </c>
       <c r="AB14" s="0">
-        <v>7.6532510318016333e-09</v>
+        <v>0</v>
       </c>
       <c r="AC14" s="0">
-        <v>-5.4001338980218847e-07</v>
+        <v>0</v>
       </c>
       <c r="AD14" s="0">
-        <v>-4.5329435839419895e-07</v>
+        <v>0</v>
       </c>
       <c r="AE14" s="0">
-        <v>-9.2975886883712645e-08</v>
+        <v>0</v>
       </c>
       <c r="AF14" s="0">
-        <v>9.3118999963134865e-08</v>
+        <v>0</v>
       </c>
       <c r="AG14" s="0">
-        <v>1.8804922835981707e-06</v>
+        <v>2.7763723056603444e-06</v>
       </c>
       <c r="AH14" s="0">
-        <v>-0.0006276836858679683</v>
+        <v>-0.000415168386239346</v>
       </c>
       <c r="AI14" s="0">
-        <v>-9.6994301454481346e-08</v>
+        <v>1.073568422298722e-07</v>
       </c>
       <c r="AJ14" s="0">
-        <v>1.3911910133611669e-07</v>
+        <v>1.2906677459321744e-07</v>
       </c>
     </row>
   </sheetData>
@@ -5086,13 +5086,13 @@
   <cols>
     <col min="1" max="1" width="5.85546875" customWidth="true"/>
     <col min="2" max="2" width="15.7109375" customWidth="true"/>
-    <col min="3" max="3" width="15.7109375" customWidth="true"/>
-    <col min="4" max="4" width="15.5703125" customWidth="true"/>
+    <col min="3" max="3" width="14.7109375" customWidth="true"/>
+    <col min="4" max="4" width="13.7109375" customWidth="true"/>
     <col min="5" max="5" width="15.7109375" customWidth="true"/>
-    <col min="6" max="6" width="15.5703125" customWidth="true"/>
-    <col min="7" max="7" width="15.7109375" customWidth="true"/>
-    <col min="8" max="8" width="15.5703125" customWidth="true"/>
-    <col min="9" max="9" width="15.7109375" customWidth="true"/>
+    <col min="6" max="6" width="15.7109375" customWidth="true"/>
+    <col min="7" max="7" width="13.7109375" customWidth="true"/>
+    <col min="8" max="8" width="13.7109375" customWidth="true"/>
+    <col min="9" max="9" width="15.5703125" customWidth="true"/>
     <col min="10" max="10" width="15.7109375" customWidth="true"/>
     <col min="11" max="11" width="15.5703125" customWidth="true"/>
     <col min="12" max="12" width="15.7109375" customWidth="true"/>
@@ -5100,26 +5100,26 @@
     <col min="14" max="14" width="15.7109375" customWidth="true"/>
     <col min="15" max="15" width="15.7109375" customWidth="true"/>
     <col min="16" max="16" width="16.42578125" customWidth="true"/>
-    <col min="17" max="17" width="15.5703125" customWidth="true"/>
-    <col min="18" max="18" width="15.7109375" customWidth="true"/>
-    <col min="19" max="19" width="15.7109375" customWidth="true"/>
-    <col min="20" max="20" width="15.7109375" customWidth="true"/>
+    <col min="17" max="17" width="14.7109375" customWidth="true"/>
+    <col min="18" max="18" width="12.7109375" customWidth="true"/>
+    <col min="19" max="19" width="12.7109375" customWidth="true"/>
+    <col min="20" max="20" width="14.7109375" customWidth="true"/>
     <col min="21" max="21" width="15.7109375" customWidth="true"/>
     <col min="22" max="22" width="15.7109375" customWidth="true"/>
     <col min="23" max="23" width="15.7109375" customWidth="true"/>
     <col min="24" max="24" width="15.7109375" customWidth="true"/>
     <col min="25" max="25" width="15.5703125" customWidth="true"/>
-    <col min="26" max="26" width="15.5703125" customWidth="true"/>
-    <col min="27" max="27" width="15.7109375" customWidth="true"/>
-    <col min="28" max="28" width="15.7109375" customWidth="true"/>
-    <col min="29" max="29" width="15.5703125" customWidth="true"/>
-    <col min="30" max="30" width="15.7109375" customWidth="true"/>
-    <col min="31" max="31" width="15.5703125" customWidth="true"/>
-    <col min="32" max="32" width="15.5703125" customWidth="true"/>
+    <col min="26" max="26" width="14.7109375" customWidth="true"/>
+    <col min="27" max="27" width="13.7109375" customWidth="true"/>
+    <col min="28" max="28" width="13.7109375" customWidth="true"/>
+    <col min="29" max="29" width="14.7109375" customWidth="true"/>
+    <col min="30" max="30" width="13.7109375" customWidth="true"/>
+    <col min="31" max="31" width="15.7109375" customWidth="true"/>
+    <col min="32" max="32" width="12.7109375" customWidth="true"/>
     <col min="33" max="33" width="15.7109375" customWidth="true"/>
     <col min="34" max="34" width="15.7109375" customWidth="true"/>
     <col min="35" max="35" width="15.7109375" customWidth="true"/>
-    <col min="36" max="36" width="15.5703125" customWidth="true"/>
+    <col min="36" max="36" width="15.7109375" customWidth="true"/>
   </cols>
   <sheetData>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="1" x14ac:dyDescent="0.3">
@@ -5237,109 +5237,109 @@
         <v>36</v>
       </c>
       <c r="B2" s="0">
-        <v>0.51340177614187332</v>
+        <v>0.51341278063261941</v>
       </c>
       <c r="C2" s="0">
-        <v>0.51453301879526492</v>
+        <v>0.51508455763192518</v>
       </c>
       <c r="D2" s="0">
-        <v>0.48763171461787536</v>
+        <v>0.49086915129061254</v>
       </c>
       <c r="E2" s="0">
-        <v>0.26971648383622643</v>
+        <v>0.26972518819761976</v>
       </c>
       <c r="F2" s="0">
-        <v>0.26654726894237618</v>
+        <v>0.26671243942007949</v>
       </c>
       <c r="G2" s="0">
-        <v>0.26552681366284164</v>
+        <v>0.26572855277509821</v>
       </c>
       <c r="H2" s="0">
-        <v>0.89783172610071771</v>
+        <v>0.89839430616516691</v>
       </c>
       <c r="I2" s="0">
-        <v>0.14723359389854304</v>
+        <v>0.14748822635653811</v>
       </c>
       <c r="J2" s="0">
-        <v>0.14453410903673081</v>
+        <v>0.1445887334960568</v>
       </c>
       <c r="K2" s="0">
-        <v>0.23134748802237537</v>
+        <v>0.23135594300118856</v>
       </c>
       <c r="L2" s="0">
-        <v>0.22937439620277561</v>
+        <v>0.22949606243216531</v>
       </c>
       <c r="M2" s="0">
-        <v>0.33055241698298032</v>
+        <v>0.33055871080990335</v>
       </c>
       <c r="N2" s="0">
-        <v>0.23582363423360669</v>
+        <v>0.23582745538052483</v>
       </c>
       <c r="O2" s="0">
-        <v>0.25613862641537144</v>
+        <v>0.25615139976407025</v>
       </c>
       <c r="P2" s="0">
-        <v>0.83710558421292458</v>
+        <v>0.83710572740979106</v>
       </c>
       <c r="Q2" s="0">
-        <v>0.52197019284050727</v>
+        <v>0.52376875513035626</v>
       </c>
       <c r="R2" s="0">
-        <v>0.52087893510064631</v>
+        <v>0.52367420323819314</v>
       </c>
       <c r="S2" s="0">
-        <v>0.5215273659820463</v>
+        <v>0.52459771943317146</v>
       </c>
       <c r="T2" s="0">
-        <v>0.9850797725084226</v>
+        <v>0.98807909320410126</v>
       </c>
       <c r="U2" s="0">
-        <v>0.22870404388091936</v>
+        <v>0.22872769603452503</v>
       </c>
       <c r="V2" s="0">
-        <v>0.22498654820589337</v>
+        <v>0.22542488289170734</v>
       </c>
       <c r="W2" s="0">
-        <v>0.21659621120636738</v>
+        <v>0.22701482312520191</v>
       </c>
       <c r="X2" s="0">
-        <v>0.98555180266367615</v>
+        <v>0.98603936660245373</v>
       </c>
       <c r="Y2" s="0">
-        <v>0.4157375248945322</v>
+        <v>0.41584700820439152</v>
       </c>
       <c r="Z2" s="0">
-        <v>0.44767958793926976</v>
+        <v>0.44775810082403611</v>
       </c>
       <c r="AA2" s="0">
-        <v>0.44031265297983807</v>
+        <v>0.44207487918355831</v>
       </c>
       <c r="AB2" s="0">
-        <v>0.7051188851913005</v>
+        <v>0.70595387404117616</v>
       </c>
       <c r="AC2" s="0">
-        <v>0.23283898597843525</v>
+        <v>0.23286228126325473</v>
       </c>
       <c r="AD2" s="0">
-        <v>0.24950459421210819</v>
+        <v>0.2497285742229462</v>
       </c>
       <c r="AE2" s="0">
-        <v>0.25076582762063276</v>
+        <v>0.25081928882345395</v>
       </c>
       <c r="AF2" s="0">
-        <v>0.71499915620682242</v>
+        <v>0.72510567626033973</v>
       </c>
       <c r="AG2" s="0">
-        <v>0.22920286857363881</v>
+        <v>0.22923820103489936</v>
       </c>
       <c r="AH2" s="0">
-        <v>0.2313471057654421</v>
+        <v>0.23139588207666961</v>
       </c>
       <c r="AI2" s="0">
-        <v>0.23290033209644606</v>
+        <v>0.23296361626696163</v>
       </c>
       <c r="AJ2" s="0">
-        <v>0.97868591206310784</v>
+        <v>0.97892906173500693</v>
       </c>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="3" x14ac:dyDescent="0.3">
@@ -5347,109 +5347,109 @@
         <v>37</v>
       </c>
       <c r="B3" s="0">
-        <v>0.48050324100899344</v>
+        <v>0.47537204545573614</v>
       </c>
       <c r="C3" s="0">
-        <v>0.48532009069755694</v>
+        <v>0.48064182420140067</v>
       </c>
       <c r="D3" s="0">
-        <v>0.46666700867940331</v>
+        <v>0.46473877026554317</v>
       </c>
       <c r="E3" s="0">
-        <v>0.49925050775724089</v>
+        <v>0.49392446687029767</v>
       </c>
       <c r="F3" s="0">
-        <v>0.49649058310575911</v>
+        <v>0.49148250062042459</v>
       </c>
       <c r="G3" s="0">
-        <v>0.48989511349799264</v>
+        <v>0.48502146041666411</v>
       </c>
       <c r="H3" s="0">
-        <v>0.077025664276189273</v>
+        <v>0.076249237411939355</v>
       </c>
       <c r="I3" s="0">
-        <v>0.39173816668153649</v>
+        <v>0.38821680891813837</v>
       </c>
       <c r="J3" s="0">
-        <v>0.38458535049825832</v>
+        <v>0.38061408018281984</v>
       </c>
       <c r="K3" s="0">
-        <v>0.46647454706429875</v>
+        <v>0.46150013508450244</v>
       </c>
       <c r="L3" s="0">
-        <v>0.45948329880565991</v>
+        <v>0.45480794174273992</v>
       </c>
       <c r="M3" s="0">
-        <v>0.27340509705335875</v>
+        <v>0.2704848125367742</v>
       </c>
       <c r="N3" s="0">
-        <v>0.47164653112117599</v>
+        <v>0.46660747374765188</v>
       </c>
       <c r="O3" s="0">
-        <v>0.46936356041766569</v>
+        <v>0.46436452650939603</v>
       </c>
       <c r="P3" s="0">
-        <v>0.17203393408855877</v>
+        <v>0.17019320010737729</v>
       </c>
       <c r="Q3" s="0">
-        <v>0.47797886246316329</v>
+        <v>0.47449384649687038</v>
       </c>
       <c r="R3" s="0">
-        <v>0.47890757600943568</v>
+        <v>0.47632579676180675</v>
       </c>
       <c r="S3" s="0">
-        <v>0.4777315850069328</v>
+        <v>0.47540228056682854</v>
       </c>
       <c r="T3" s="0">
-        <v>0.0094900258698734363</v>
+        <v>0.0094170681664663032</v>
       </c>
       <c r="U3" s="0">
-        <v>0.46030542908443983</v>
+        <v>0.45542725557597313</v>
       </c>
       <c r="V3" s="0">
-        <v>0.45931473599353229</v>
+        <v>0.45528536262941027</v>
       </c>
       <c r="W3" s="0">
-        <v>0.43681900145184238</v>
+        <v>0.45293188117439948</v>
       </c>
       <c r="X3" s="0">
-        <v>0.013241419537405447</v>
+        <v>0.013106216940277107</v>
       </c>
       <c r="Y3" s="0">
-        <v>0.47962543957745507</v>
+        <v>0.47461840389104376</v>
       </c>
       <c r="Z3" s="0">
-        <v>0.48620062161696687</v>
+        <v>0.48108263119532724</v>
       </c>
       <c r="AA3" s="0">
-        <v>0.47740221321854703</v>
+        <v>0.47418423202749999</v>
       </c>
       <c r="AB3" s="0">
-        <v>0.28351977529314643</v>
+        <v>0.28081826020840456</v>
       </c>
       <c r="AC3" s="0">
-        <v>0.46346151722510248</v>
+        <v>0.45854835166024244</v>
       </c>
       <c r="AD3" s="0">
-        <v>0.48048163565442464</v>
+        <v>0.47576719480196411</v>
       </c>
       <c r="AE3" s="0">
-        <v>0.4787920917292201</v>
+        <v>0.47376999866892661</v>
       </c>
       <c r="AF3" s="0">
-        <v>0.24150419328842468</v>
+        <v>0.24229723634398459</v>
       </c>
       <c r="AG3" s="0">
-        <v>0.45995341217920305</v>
+        <v>0.45510205550370414</v>
       </c>
       <c r="AH3" s="0">
-        <v>0.45882178770390192</v>
+        <v>0.45400809567427813</v>
       </c>
       <c r="AI3" s="0">
-        <v>0.45105542272919963</v>
+        <v>0.44635038002830935</v>
       </c>
       <c r="AJ3" s="0">
-        <v>0.015089323460651352</v>
+        <v>0.014931576454482929</v>
       </c>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="4" x14ac:dyDescent="0.3">
@@ -5457,52 +5457,52 @@
         <v>38</v>
       </c>
       <c r="B4" s="0">
-        <v>0.0055648588653724696</v>
+        <v>0.010533005633545632</v>
       </c>
       <c r="C4" s="0">
-        <v>0</v>
+        <v>0.0042736181666740911</v>
       </c>
       <c r="D4" s="0">
-        <v>0.040011045934653301</v>
+        <v>0.044392078443844262</v>
       </c>
       <c r="E4" s="0">
-        <v>0.22966008655963729</v>
+        <v>0.23006390017610842</v>
       </c>
       <c r="F4" s="0">
-        <v>0.23687977661279899</v>
+        <v>0.23724019460901322</v>
       </c>
       <c r="G4" s="0">
-        <v>0.23196017328926979</v>
+        <v>0.23238499726050146</v>
       </c>
       <c r="H4" s="0">
-        <v>0.025058607351146137</v>
+        <v>0.025356456422893775</v>
       </c>
       <c r="I4" s="0">
-        <v>0.35515130913451809</v>
+        <v>0.35234679316177953</v>
       </c>
       <c r="J4" s="0">
-        <v>0.35591672937247854</v>
+        <v>0.35254508103682558</v>
       </c>
       <c r="K4" s="0">
-        <v>0.26938785159053846</v>
+        <v>0.26860148089353481</v>
       </c>
       <c r="L4" s="0">
-        <v>0.27087307195040056</v>
+        <v>0.27011446540261075</v>
       </c>
       <c r="M4" s="0">
-        <v>0.15183334809063811</v>
+        <v>0.15149851475714193</v>
       </c>
       <c r="N4" s="0">
-        <v>0.26313256888547043</v>
+        <v>0.26252853081914923</v>
       </c>
       <c r="O4" s="0">
-        <v>0.24677530895096339</v>
+        <v>0.24650331554042285</v>
       </c>
       <c r="P4" s="0">
-        <v>-0.030386515231548131</v>
+        <v>-0.027918660603906215</v>
       </c>
       <c r="Q4" s="0">
-        <v>0</v>
+        <v>0.0017373983727732962</v>
       </c>
       <c r="R4" s="0">
         <v>0</v>
@@ -5511,55 +5511,55 @@
         <v>0</v>
       </c>
       <c r="T4" s="0">
-        <v>0.0024478859475978096</v>
+        <v>0.0025038386294324367</v>
       </c>
       <c r="U4" s="0">
-        <v>0.27182018831034832</v>
+        <v>0.27093494139478691</v>
       </c>
       <c r="V4" s="0">
-        <v>0.275790341201956</v>
+        <v>0.27531743373325196</v>
       </c>
       <c r="W4" s="0">
-        <v>0.26137057915525624</v>
+        <v>0.27295826388621086</v>
       </c>
       <c r="X4" s="0">
-        <v>0.00072935141441461486</v>
+        <v>0.00085441645726914007</v>
       </c>
       <c r="Y4" s="0">
-        <v>0.098172105090803985</v>
+        <v>0.1011861817343294</v>
       </c>
       <c r="Z4" s="0">
-        <v>0.064315368557667577</v>
+        <v>0.068105006664249221</v>
       </c>
       <c r="AA4" s="0">
-        <v>0.068854615776939701</v>
+        <v>0.072732486800085705</v>
       </c>
       <c r="AB4" s="0">
-        <v>0.010433092356879531</v>
+        <v>0.01322786575041918</v>
       </c>
       <c r="AC4" s="0">
-        <v>0.26620126157982815</v>
+        <v>0.26546756557102436</v>
       </c>
       <c r="AD4" s="0">
-        <v>0.25337067044304101</v>
+        <v>0.25329086466972206</v>
       </c>
       <c r="AE4" s="0">
-        <v>0.25208606732647743</v>
+        <v>0.25184222453223998</v>
       </c>
       <c r="AF4" s="0">
-        <v>0.030229760128644118</v>
+        <v>0.032597087395675732</v>
       </c>
       <c r="AG4" s="0">
-        <v>0.27174797594456135</v>
+        <v>0.2708742729541796</v>
       </c>
       <c r="AH4" s="0">
-        <v>0.27166418569331985</v>
+        <v>0.2707956190193902</v>
       </c>
       <c r="AI4" s="0">
-        <v>0.26950611126515467</v>
+        <v>0.26861715732097491</v>
       </c>
       <c r="AJ4" s="0">
-        <v>0.0013000843053408966</v>
+        <v>0.0014324953402246321</v>
       </c>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="5" x14ac:dyDescent="0.3">
@@ -5567,106 +5567,106 @@
         <v>39</v>
       </c>
       <c r="B5" s="0">
-        <v>0.00052794261859322633</v>
+        <v>0.00068216827809869244</v>
       </c>
       <c r="C5" s="0">
-        <v>0.00012586305838938026</v>
+        <v>0</v>
       </c>
       <c r="D5" s="0">
-        <v>0.0039490047115160873</v>
+        <v>0</v>
       </c>
       <c r="E5" s="0">
-        <v>0.0010161523766406835</v>
+        <v>0.0058507314620216636</v>
       </c>
       <c r="F5" s="0">
-        <v>0</v>
+        <v>0.0044330919845435102</v>
       </c>
       <c r="G5" s="0">
-        <v>0.010665192660027405</v>
+        <v>0.01525184466820452</v>
       </c>
       <c r="H5" s="0">
         <v>0</v>
       </c>
       <c r="I5" s="0">
-        <v>0.10568747801927875</v>
+        <v>0.11000383142714872</v>
       </c>
       <c r="J5" s="0">
-        <v>0.11421160219542313</v>
+        <v>0.1181271800603019</v>
       </c>
       <c r="K5" s="0">
-        <v>0.031657641465172075</v>
+        <v>0.036348620620985317</v>
       </c>
       <c r="L5" s="0">
-        <v>0.037140582247217856</v>
+        <v>0.041708534038100285</v>
       </c>
       <c r="M5" s="0">
-        <v>0.12019777356330051</v>
+        <v>0.11959387844762406</v>
       </c>
       <c r="N5" s="0">
-        <v>0.028192424954430535</v>
+        <v>0.032862227804558393</v>
       </c>
       <c r="O5" s="0">
-        <v>0.01862225850850124</v>
+        <v>0.023253762421189164</v>
       </c>
       <c r="P5" s="0">
-        <v>-0.0073045784774448015</v>
+        <v>-0.0076895474297222271</v>
       </c>
       <c r="Q5" s="0">
-        <v>1.5041199633413247e-05</v>
+        <v>0</v>
       </c>
       <c r="R5" s="0">
         <v>0</v>
       </c>
       <c r="S5" s="0">
-        <v>0.00042512987483786784</v>
+        <v>0</v>
       </c>
       <c r="T5" s="0">
-        <v>0.0022487011334379066</v>
+        <v>0</v>
       </c>
       <c r="U5" s="0">
-        <v>0.037889085327484945</v>
+        <v>0.04243547289584463</v>
       </c>
       <c r="V5" s="0">
-        <v>0.036830029342260762</v>
+        <v>0.041569533844252632</v>
       </c>
       <c r="W5" s="0">
-        <v>0.037101559085973762</v>
+        <v>0.043440713537564055</v>
       </c>
       <c r="X5" s="0">
         <v>0</v>
       </c>
       <c r="Y5" s="0">
-        <v>0.0064012466654529421</v>
+        <v>0.0083106348846243156</v>
       </c>
       <c r="Z5" s="0">
-        <v>0.0017057752632187342</v>
+        <v>0.0030542613163875212</v>
       </c>
       <c r="AA5" s="0">
-        <v>0.0097788770394743544</v>
+        <v>0.011008401988855972</v>
       </c>
       <c r="AB5" s="0">
-        <v>0.00058115888773683469</v>
+        <v>0</v>
       </c>
       <c r="AC5" s="0">
-        <v>0.035968537999299603</v>
+        <v>0.04045824901156251</v>
       </c>
       <c r="AD5" s="0">
-        <v>0.016352518209217064</v>
+        <v>0.021213366305367538</v>
       </c>
       <c r="AE5" s="0">
-        <v>0.018075652235964895</v>
+        <v>0.022840522976543938</v>
       </c>
       <c r="AF5" s="0">
-        <v>0.0076844590049161363</v>
+        <v>0</v>
       </c>
       <c r="AG5" s="0">
-        <v>0.036438630099431629</v>
+        <v>0.041031464577723845</v>
       </c>
       <c r="AH5" s="0">
-        <v>0.035315499229242882</v>
+        <v>0.03994421443492055</v>
       </c>
       <c r="AI5" s="0">
-        <v>0.042195628071125174</v>
+        <v>0.046563995529792096</v>
       </c>
       <c r="AJ5" s="0">
         <v>0</v>
@@ -5683,103 +5683,103 @@
         <v>0</v>
       </c>
       <c r="D6" s="0">
-        <v>0.0017314789834959557</v>
+        <v>0</v>
       </c>
       <c r="E6" s="0">
-        <v>0.00033821159435510272</v>
+        <v>0.00043337078231809348</v>
       </c>
       <c r="F6" s="0">
-        <v>7.3401883333798764e-05</v>
+        <v>0.00013177336593910203</v>
       </c>
       <c r="G6" s="0">
-        <v>0.0012547167164277452</v>
+        <v>0.0016131448795317868</v>
       </c>
       <c r="H6" s="0">
         <v>0</v>
       </c>
       <c r="I6" s="0">
-        <v>0</v>
+        <v>0.0019424251121970422</v>
       </c>
       <c r="J6" s="0">
-        <v>0.00014684772981160592</v>
+        <v>0.0038119760558265746</v>
       </c>
       <c r="K6" s="0">
-        <v>0.0011205106551378766</v>
+        <v>0.002148455801638206</v>
       </c>
       <c r="L6" s="0">
-        <v>0.0021055588029210721</v>
+        <v>0.0032645716799449939</v>
       </c>
       <c r="M6" s="0">
-        <v>0.099983625329077036</v>
+        <v>0.099561603489366962</v>
       </c>
       <c r="N6" s="0">
-        <v>0.00065846316290110165</v>
+        <v>0.001596018718504976</v>
       </c>
       <c r="O6" s="0">
-        <v>0.00083561867677364038</v>
+        <v>0.001462812196285892</v>
       </c>
       <c r="P6" s="0">
-        <v>-0.00048564067025207332</v>
+        <v>-0.0007022233179339516</v>
       </c>
       <c r="Q6" s="0">
         <v>0</v>
       </c>
       <c r="R6" s="0">
-        <v>3.3878867124713006e-05</v>
+        <v>0</v>
       </c>
       <c r="S6" s="0">
-        <v>0.00017167474138064876</v>
+        <v>0</v>
       </c>
       <c r="T6" s="0">
-        <v>0.00045689335501688459</v>
+        <v>0</v>
       </c>
       <c r="U6" s="0">
-        <v>0.0010121565025293453</v>
+        <v>0.0022393053888035527</v>
       </c>
       <c r="V6" s="0">
-        <v>0.00052949802213182382</v>
+        <v>0.0017485613103934937</v>
       </c>
       <c r="W6" s="0">
-        <v>0.001603268277608565</v>
+        <v>0.0029108622549912375</v>
       </c>
       <c r="X6" s="0">
-        <v>0.0001166580866676894</v>
+        <v>0</v>
       </c>
       <c r="Y6" s="0">
-        <v>0</v>
+        <v>3.7771285610959899e-05</v>
       </c>
       <c r="Z6" s="0">
         <v>0</v>
       </c>
       <c r="AA6" s="0">
-        <v>0.0030376220660998264</v>
+        <v>0</v>
       </c>
       <c r="AB6" s="0">
-        <v>0.00023620761738220466</v>
+        <v>0</v>
       </c>
       <c r="AC6" s="0">
-        <v>0.0015193055311609343</v>
+        <v>0.0026635524939157612</v>
       </c>
       <c r="AD6" s="0">
         <v>0</v>
       </c>
       <c r="AE6" s="0">
-        <v>8.4234660735750693e-05</v>
+        <v>0.0007279649988354358</v>
       </c>
       <c r="AF6" s="0">
-        <v>0.0037914413602215019</v>
+        <v>0</v>
       </c>
       <c r="AG6" s="0">
-        <v>0.0021008197627635219</v>
+        <v>0.0032372781024048022</v>
       </c>
       <c r="AH6" s="0">
-        <v>0.00042077262933489607</v>
+        <v>0.0015928908191306138</v>
       </c>
       <c r="AI6" s="0">
-        <v>0.0039440776475344261</v>
+        <v>0.0051819768694500524</v>
       </c>
       <c r="AJ6" s="0">
-        <v>0.0010079966494154966</v>
+        <v>0.000960640769860447</v>
       </c>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="7" x14ac:dyDescent="0.3">
@@ -5796,76 +5796,76 @@
         <v>0</v>
       </c>
       <c r="E7" s="0">
-        <v>0</v>
+        <v>2.3425116344709864e-06</v>
       </c>
       <c r="F7" s="0">
         <v>0</v>
       </c>
       <c r="G7" s="0">
-        <v>0.00061253848492076569</v>
+        <v>0</v>
       </c>
       <c r="H7" s="0">
-        <v>6.0987388167699864e-05</v>
+        <v>0</v>
       </c>
       <c r="I7" s="0">
-        <v>0</v>
+        <v>1.9150241981996001e-06</v>
       </c>
       <c r="J7" s="0">
-        <v>0.00024179593462003607</v>
+        <v>0.00031294916816916081</v>
       </c>
       <c r="K7" s="0">
-        <v>0</v>
+        <v>4.5364598150730737e-05</v>
       </c>
       <c r="L7" s="0">
-        <v>0.00052316859999306019</v>
+        <v>0.00060842470443880448</v>
       </c>
       <c r="M7" s="0">
-        <v>0.021897842693349011</v>
+        <v>0.024931328865245853</v>
       </c>
       <c r="N7" s="0">
-        <v>0.00026101678182951469</v>
+        <v>0.00029436759056704923</v>
       </c>
       <c r="O7" s="0">
-        <v>0.0047726510808730974</v>
+        <v>0.004570782088622714</v>
       </c>
       <c r="P7" s="0">
-        <v>0.039991419966531418</v>
+        <v>0.037872272423713618</v>
       </c>
       <c r="Q7" s="0">
-        <v>8.8992772260407046e-07</v>
+        <v>0</v>
       </c>
       <c r="R7" s="0">
         <v>0</v>
       </c>
       <c r="S7" s="0">
-        <v>0.00010974007385307078</v>
+        <v>0</v>
       </c>
       <c r="T7" s="0">
-        <v>0.00025931244667422505</v>
+        <v>0</v>
       </c>
       <c r="U7" s="0">
-        <v>0</v>
+        <v>3.9184706722363502e-05</v>
       </c>
       <c r="V7" s="0">
-        <v>0.00014158615114345349</v>
+        <v>0.00018205885495635227</v>
       </c>
       <c r="W7" s="0">
-        <v>0.000442719911848022</v>
+        <v>0.00053579154091609607</v>
       </c>
       <c r="X7" s="0">
-        <v>0.00035232654801421021</v>
+        <v>0</v>
       </c>
       <c r="Y7" s="0">
         <v>0</v>
       </c>
       <c r="Z7" s="0">
-        <v>2.1957777615410198e-05</v>
+        <v>0</v>
       </c>
       <c r="AA7" s="0">
-        <v>0.00048403184115365861</v>
+        <v>0</v>
       </c>
       <c r="AB7" s="0">
-        <v>7.4483196176604988e-05</v>
+        <v>0</v>
       </c>
       <c r="AC7" s="0">
         <v>0</v>
@@ -5874,22 +5874,22 @@
         <v>0</v>
       </c>
       <c r="AE7" s="0">
-        <v>8.8248191679392193e-05</v>
+        <v>0</v>
       </c>
       <c r="AF7" s="0">
-        <v>0.0017004984162826708</v>
+        <v>0</v>
       </c>
       <c r="AG7" s="0">
         <v>0</v>
       </c>
       <c r="AH7" s="0">
-        <v>0</v>
+        <v>3.120674192562027e-05</v>
       </c>
       <c r="AI7" s="0">
         <v>0</v>
       </c>
       <c r="AJ7" s="0">
-        <v>0.0038404288752120494</v>
+        <v>0.0036814423403646853</v>
       </c>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="8" x14ac:dyDescent="0.3">
@@ -5906,13 +5906,13 @@
         <v>0</v>
       </c>
       <c r="E8" s="0">
-        <v>6.9664378638310144e-06</v>
+        <v>0</v>
       </c>
       <c r="F8" s="0">
-        <v>2.5263820743141506e-06</v>
+        <v>0</v>
       </c>
       <c r="G8" s="0">
-        <v>1.7039304138835204e-05</v>
+        <v>0</v>
       </c>
       <c r="H8" s="0">
         <v>0</v>
@@ -5921,28 +5921,28 @@
         <v>0</v>
       </c>
       <c r="J8" s="0">
-        <v>0.00011131706052849998</v>
+        <v>0</v>
       </c>
       <c r="K8" s="0">
         <v>0</v>
       </c>
       <c r="L8" s="0">
-        <v>0.00011745731185391115</v>
+        <v>0</v>
       </c>
       <c r="M8" s="0">
-        <v>0.0019150342741729039</v>
+        <v>0.0030166586961654909</v>
       </c>
       <c r="N8" s="0">
-        <v>7.1364872581939216e-05</v>
+        <v>8.1211975833658229e-05</v>
       </c>
       <c r="O8" s="0">
-        <v>0.0029414988187133396</v>
+        <v>0.0030009030503579102</v>
       </c>
       <c r="P8" s="0">
-        <v>-0.010299448713858064</v>
+        <v>-0.0076287849839246592</v>
       </c>
       <c r="Q8" s="0">
-        <v>3.3391023827474175e-06</v>
+        <v>0</v>
       </c>
       <c r="R8" s="0">
         <v>0</v>
@@ -5954,25 +5954,25 @@
         <v>0</v>
       </c>
       <c r="U8" s="0">
-        <v>0.00014554869634715253</v>
+        <v>0.00013649976273813269</v>
       </c>
       <c r="V8" s="0">
-        <v>0.00026244430051717811</v>
+        <v>0.00025474854351620362</v>
       </c>
       <c r="W8" s="0">
-        <v>0.00011435739134435379</v>
+        <v>0.00013821273233888707</v>
       </c>
       <c r="X8" s="0">
         <v>0</v>
       </c>
       <c r="Y8" s="0">
-        <v>3.4149405300185531e-05</v>
+        <v>0</v>
       </c>
       <c r="Z8" s="0">
-        <v>1.3998965406846254e-05</v>
+        <v>0</v>
       </c>
       <c r="AA8" s="0">
-        <v>9.825523514644874e-05</v>
+        <v>0</v>
       </c>
       <c r="AB8" s="0">
         <v>0</v>
@@ -5981,10 +5981,10 @@
         <v>0</v>
       </c>
       <c r="AD8" s="0">
-        <v>0.00013113587583772851</v>
+        <v>0</v>
       </c>
       <c r="AE8" s="0">
-        <v>2.9186672658201442e-05</v>
+        <v>0</v>
       </c>
       <c r="AF8" s="0">
         <v>0</v>
@@ -5993,10 +5993,10 @@
         <v>0</v>
       </c>
       <c r="AH8" s="0">
-        <v>0.00013485988753134625</v>
+        <v>0.00012677437222847484</v>
       </c>
       <c r="AI8" s="0">
-        <v>0.00027508763919824721</v>
+        <v>0.00021761102247546627</v>
       </c>
       <c r="AJ8" s="0">
         <v>0</v>
@@ -6010,73 +6010,73 @@
         <v>0</v>
       </c>
       <c r="C9" s="0">
-        <v>1.6843607683067987e-05</v>
+        <v>0</v>
       </c>
       <c r="D9" s="0">
-        <v>7.1129349339018729e-06</v>
+        <v>0</v>
       </c>
       <c r="E9" s="0">
-        <v>2.8182181285944444e-06</v>
+        <v>0</v>
       </c>
       <c r="F9" s="0">
-        <v>5.6351530745796031e-06</v>
+        <v>0</v>
       </c>
       <c r="G9" s="0">
-        <v>6.7897906055222959e-05</v>
+        <v>0</v>
       </c>
       <c r="H9" s="0">
-        <v>1.658125126851996e-05</v>
+        <v>0</v>
       </c>
       <c r="I9" s="0">
-        <v>0.0001068920542690897</v>
+        <v>0</v>
       </c>
       <c r="J9" s="0">
-        <v>0.000226336141238114</v>
+        <v>0</v>
       </c>
       <c r="K9" s="0">
         <v>0</v>
       </c>
       <c r="L9" s="0">
-        <v>0.00037982333678676807</v>
+        <v>0</v>
       </c>
       <c r="M9" s="0">
-        <v>0.00014527217492889852</v>
+        <v>0.0002880065964934178</v>
       </c>
       <c r="N9" s="0">
-        <v>0.00020928400997444172</v>
+        <v>0.0001988472236151441</v>
       </c>
       <c r="O9" s="0">
-        <v>0.00054061266642170178</v>
+        <v>0.00068626245630293769</v>
       </c>
       <c r="P9" s="0">
-        <v>-0.0013455534132147927</v>
+        <v>-0.0018027733573175563</v>
       </c>
       <c r="Q9" s="0">
         <v>0</v>
       </c>
       <c r="R9" s="0">
-        <v>0.00013127892983215759</v>
+        <v>0</v>
       </c>
       <c r="S9" s="0">
-        <v>2.5044765740667089e-05</v>
+        <v>0</v>
       </c>
       <c r="T9" s="0">
-        <v>6.1960980113490847e-06</v>
+        <v>0</v>
       </c>
       <c r="U9" s="0">
-        <v>5.3187472596911614e-05</v>
+        <v>5.8077193810438753e-05</v>
       </c>
       <c r="V9" s="0">
-        <v>0.00021666614915683894</v>
+        <v>0.00021741819251177969</v>
       </c>
       <c r="W9" s="0">
-        <v>6.320055113150761e-05</v>
+        <v>6.9451748377582029e-05</v>
       </c>
       <c r="X9" s="0">
         <v>0</v>
       </c>
       <c r="Y9" s="0">
-        <v>1.5048439181455557e-05</v>
+        <v>0</v>
       </c>
       <c r="Z9" s="0">
         <v>0</v>
@@ -6085,22 +6085,22 @@
         <v>0</v>
       </c>
       <c r="AB9" s="0">
-        <v>2.5906339128246704e-05</v>
+        <v>0</v>
       </c>
       <c r="AC9" s="0">
-        <v>2.7803424900959812e-06</v>
+        <v>0</v>
       </c>
       <c r="AD9" s="0">
-        <v>0.00013261228335965591</v>
+        <v>0</v>
       </c>
       <c r="AE9" s="0">
-        <v>7.411241243777455e-05</v>
+        <v>0</v>
       </c>
       <c r="AF9" s="0">
-        <v>2.2737189300523647e-05</v>
+        <v>0</v>
       </c>
       <c r="AG9" s="0">
-        <v>0.00020993394288234613</v>
+        <v>0.00018816241885009376</v>
       </c>
       <c r="AH9" s="0">
         <v>0</v>
@@ -6117,16 +6117,16 @@
         <v>44</v>
       </c>
       <c r="B10" s="0">
-        <v>1.9969173456526292e-06</v>
+        <v>0</v>
       </c>
       <c r="C10" s="0">
-        <v>4.1152948201133191e-06</v>
+        <v>0</v>
       </c>
       <c r="D10" s="0">
-        <v>2.6168028224857289e-06</v>
+        <v>0</v>
       </c>
       <c r="E10" s="0">
-        <v>8.5774037711061185e-06</v>
+        <v>0</v>
       </c>
       <c r="F10" s="0">
         <v>0</v>
@@ -6135,22 +6135,22 @@
         <v>0</v>
       </c>
       <c r="H10" s="0">
-        <v>6.34524161277727e-06</v>
+        <v>0</v>
       </c>
       <c r="I10" s="0">
-        <v>8.0608785731303898e-05</v>
+        <v>0</v>
       </c>
       <c r="J10" s="0">
-        <v>2.4955161865646779e-05</v>
+        <v>0</v>
       </c>
       <c r="K10" s="0">
-        <v>7.9899966960371445e-06</v>
+        <v>0</v>
       </c>
       <c r="L10" s="0">
-        <v>6.9359197962992372e-07</v>
+        <v>0</v>
       </c>
       <c r="M10" s="0">
-        <v>4.4572075623724052e-05</v>
+        <v>5.6239766940134245e-05</v>
       </c>
       <c r="N10" s="0">
         <v>0</v>
@@ -6159,19 +6159,19 @@
         <v>0</v>
       </c>
       <c r="P10" s="0">
-        <v>0.0007106709324315784</v>
+        <v>0.00053700593444923263</v>
       </c>
       <c r="Q10" s="0">
-        <v>2.4366307758453372e-05</v>
+        <v>0</v>
       </c>
       <c r="R10" s="0">
-        <v>4.7265820663127097e-05</v>
+        <v>0</v>
       </c>
       <c r="S10" s="0">
-        <v>9.3330359961600629e-06</v>
+        <v>0</v>
       </c>
       <c r="T10" s="0">
-        <v>1.1112570010813266e-05</v>
+        <v>0</v>
       </c>
       <c r="U10" s="0">
         <v>0</v>
@@ -6183,22 +6183,22 @@
         <v>0</v>
       </c>
       <c r="X10" s="0">
-        <v>8.3815727215549887e-06</v>
+        <v>0</v>
       </c>
       <c r="Y10" s="0">
         <v>0</v>
       </c>
       <c r="Z10" s="0">
-        <v>4.6370142866194527e-05</v>
+        <v>0</v>
       </c>
       <c r="AA10" s="0">
-        <v>2.0586319492472984e-05</v>
+        <v>0</v>
       </c>
       <c r="AB10" s="0">
-        <v>1.0353844900745796e-05</v>
+        <v>0</v>
       </c>
       <c r="AC10" s="0">
-        <v>1.364887754151173e-06</v>
+        <v>0</v>
       </c>
       <c r="AD10" s="0">
         <v>0</v>
@@ -6207,19 +6207,19 @@
         <v>0</v>
       </c>
       <c r="AF10" s="0">
-        <v>6.7185564392639803e-05</v>
+        <v>0</v>
       </c>
       <c r="AG10" s="0">
-        <v>0.00033137887230666886</v>
+        <v>0.00031844212167955727</v>
       </c>
       <c r="AH10" s="0">
-        <v>0.0003504582581733778</v>
+        <v>0.00031818192089000879</v>
       </c>
       <c r="AI10" s="0">
-        <v>0.00012135749112290226</v>
+        <v>0.00010369191744208546</v>
       </c>
       <c r="AJ10" s="0">
-        <v>7.5859551217222061e-05</v>
+        <v>5.9427896515243619e-05</v>
       </c>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="11" x14ac:dyDescent="0.3">
@@ -6227,7 +6227,7 @@
         <v>45</v>
       </c>
       <c r="B11" s="0">
-        <v>1.780124103997523e-07</v>
+        <v>0</v>
       </c>
       <c r="C11" s="0">
         <v>0</v>
@@ -6239,7 +6239,7 @@
         <v>0</v>
       </c>
       <c r="F11" s="0">
-        <v>5.5415676249715856e-07</v>
+        <v>0</v>
       </c>
       <c r="G11" s="0">
         <v>0</v>
@@ -6254,7 +6254,7 @@
         <v>0</v>
       </c>
       <c r="K11" s="0">
-        <v>3.9312753780280794e-06</v>
+        <v>0</v>
       </c>
       <c r="L11" s="0">
         <v>0</v>
@@ -6266,13 +6266,13 @@
         <v>0</v>
       </c>
       <c r="O11" s="0">
-        <v>2.1654755062388935e-06</v>
+        <v>0</v>
       </c>
       <c r="P11" s="0">
-        <v>1.141161157371172e-05</v>
+        <v>6.1547340460401867e-05</v>
       </c>
       <c r="Q11" s="0">
-        <v>7.1256761306307107e-06</v>
+        <v>0</v>
       </c>
       <c r="R11" s="0">
         <v>0</v>
@@ -6284,25 +6284,25 @@
         <v>0</v>
       </c>
       <c r="U11" s="0">
-        <v>7.0166198619692495e-06</v>
+        <v>1.567046795798855e-06</v>
       </c>
       <c r="V11" s="0">
-        <v>5.803710674264131e-05</v>
+        <v>0</v>
       </c>
       <c r="W11" s="0">
-        <v>6.2356496540603585e-07</v>
+        <v>0</v>
       </c>
       <c r="X11" s="0">
         <v>0</v>
       </c>
       <c r="Y11" s="0">
-        <v>1.0707242635636249e-05</v>
+        <v>0</v>
       </c>
       <c r="Z11" s="0">
-        <v>1.5954085638950755e-05</v>
+        <v>0</v>
       </c>
       <c r="AA11" s="0">
-        <v>1.102838168059839e-05</v>
+        <v>0</v>
       </c>
       <c r="AB11" s="0">
         <v>0</v>
@@ -6311,10 +6311,10 @@
         <v>0</v>
       </c>
       <c r="AD11" s="0">
-        <v>1.6405652555742528e-05</v>
+        <v>0</v>
       </c>
       <c r="AE11" s="0">
-        <v>2.1628469609899888e-06</v>
+        <v>0</v>
       </c>
       <c r="AF11" s="0">
         <v>0</v>
@@ -6329,7 +6329,7 @@
         <v>0</v>
       </c>
       <c r="AJ11" s="0">
-        <v>0</v>
+        <v>5.2265504401925914e-06</v>
       </c>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="12" x14ac:dyDescent="0.3">
@@ -6349,10 +6349,10 @@
         <v>0</v>
       </c>
       <c r="F12" s="0">
-        <v>2.5376382035782547e-07</v>
+        <v>0</v>
       </c>
       <c r="G12" s="0">
-        <v>5.1290152941601328e-07</v>
+        <v>0</v>
       </c>
       <c r="H12" s="0">
         <v>0</v>
@@ -6361,25 +6361,25 @@
         <v>0</v>
       </c>
       <c r="J12" s="0">
-        <v>4.8023665709474409e-07</v>
+        <v>0</v>
       </c>
       <c r="K12" s="0">
         <v>0</v>
       </c>
       <c r="L12" s="0">
-        <v>1.4169512950484454e-06</v>
+        <v>0</v>
       </c>
       <c r="M12" s="0">
-        <v>1.6593005617275063e-05</v>
+        <v>1.8677089239847753e-06</v>
       </c>
       <c r="N12" s="0">
-        <v>4.7119780293106881e-06</v>
+        <v>3.5679062555574575e-06</v>
       </c>
       <c r="O12" s="0">
-        <v>7.6989892103990575e-06</v>
+        <v>6.2359733522136903e-06</v>
       </c>
       <c r="P12" s="0">
-        <v>-3.4461907779678922e-05</v>
+        <v>-2.7405645040689532e-05</v>
       </c>
       <c r="Q12" s="0">
         <v>0</v>
@@ -6394,19 +6394,19 @@
         <v>0</v>
       </c>
       <c r="U12" s="0">
-        <v>3.1304750426438029e-06</v>
+        <v>0</v>
       </c>
       <c r="V12" s="0">
-        <v>0.00063417715293568352</v>
+        <v>0</v>
       </c>
       <c r="W12" s="0">
-        <v>0.0041198240106591335</v>
+        <v>0</v>
       </c>
       <c r="X12" s="0">
         <v>0</v>
       </c>
       <c r="Y12" s="0">
-        <v>3.7786846385805152e-06</v>
+        <v>0</v>
       </c>
       <c r="Z12" s="0">
         <v>0</v>
@@ -6418,13 +6418,13 @@
         <v>0</v>
       </c>
       <c r="AC12" s="0">
-        <v>4.9384649652868639e-06</v>
+        <v>0</v>
       </c>
       <c r="AD12" s="0">
-        <v>1.0427669455892746e-05</v>
+        <v>0</v>
       </c>
       <c r="AE12" s="0">
-        <v>2.4163032326494116e-06</v>
+        <v>0</v>
       </c>
       <c r="AF12" s="0">
         <v>0</v>
@@ -6433,7 +6433,7 @@
         <v>0</v>
       </c>
       <c r="AH12" s="0">
-        <v>0.00067769218662345554</v>
+        <v>0.00059628523457812808</v>
       </c>
       <c r="AI12" s="0">
         <v>0</v>
@@ -6450,70 +6450,70 @@
         <v>0</v>
       </c>
       <c r="C13" s="0">
-        <v>6.7054545278855744e-08</v>
+        <v>0</v>
       </c>
       <c r="D13" s="0">
-        <v>1.5830908914791125e-08</v>
+        <v>0</v>
       </c>
       <c r="E13" s="0">
-        <v>1.9581613610133728e-07</v>
+        <v>0</v>
       </c>
       <c r="F13" s="0">
         <v>0</v>
       </c>
       <c r="G13" s="0">
-        <v>1.5767964491553504e-09</v>
+        <v>0</v>
       </c>
       <c r="H13" s="0">
-        <v>8.4001804521334555e-08</v>
+        <v>0</v>
       </c>
       <c r="I13" s="0">
-        <v>1.9514261231034931e-06</v>
+        <v>0</v>
       </c>
       <c r="J13" s="0">
-        <v>4.7663238827966755e-07</v>
+        <v>0</v>
       </c>
       <c r="K13" s="0">
         <v>0</v>
       </c>
       <c r="L13" s="0">
-        <v>5.3219911634662445e-07</v>
+        <v>0</v>
       </c>
       <c r="M13" s="0">
-        <v>8.4247569535448711e-06</v>
+        <v>8.378325420619454e-06</v>
       </c>
       <c r="N13" s="0">
-        <v>0</v>
+        <v>2.9883333934014098e-07</v>
       </c>
       <c r="O13" s="0">
         <v>0</v>
       </c>
       <c r="P13" s="0">
-        <v>1.7994952665332306e-06</v>
+        <v>-1.5672052676757694e-06</v>
       </c>
       <c r="Q13" s="0">
         <v>0</v>
       </c>
       <c r="R13" s="0">
-        <v>1.0329593668427405e-06</v>
+        <v>0</v>
       </c>
       <c r="S13" s="0">
-        <v>1.2072015115271089e-07</v>
+        <v>0</v>
       </c>
       <c r="T13" s="0">
-        <v>8.5339334867341794e-08</v>
+        <v>0</v>
       </c>
       <c r="U13" s="0">
         <v>0</v>
       </c>
       <c r="V13" s="0">
-        <v>0.0012359363737299519</v>
+        <v>0</v>
       </c>
       <c r="W13" s="0">
-        <v>0.041768655393003305</v>
+        <v>0</v>
       </c>
       <c r="X13" s="0">
-        <v>4.7181635184449118e-08</v>
+        <v>0</v>
       </c>
       <c r="Y13" s="0">
         <v>0</v>
@@ -6525,10 +6525,10 @@
         <v>0</v>
       </c>
       <c r="AB13" s="0">
-        <v>1.2962163591150544e-07</v>
+        <v>0</v>
       </c>
       <c r="AC13" s="0">
-        <v>1.3079909639594289e-06</v>
+        <v>0</v>
       </c>
       <c r="AD13" s="0">
         <v>0</v>
@@ -6537,19 +6537,19 @@
         <v>0</v>
       </c>
       <c r="AF13" s="0">
-        <v>4.758305791843558e-07</v>
+        <v>0</v>
       </c>
       <c r="AG13" s="0">
-        <v>1.3100932691016686e-05</v>
+        <v>7.3476680795271229e-06</v>
       </c>
       <c r="AH13" s="0">
-        <v>0.0012676386464302004</v>
+        <v>0.001190849705988284</v>
       </c>
       <c r="AI13" s="0">
-        <v>1.9830602188757736e-06</v>
+        <v>1.4637708614884576e-06</v>
       </c>
       <c r="AJ13" s="0">
-        <v>2.5617610284836597e-07</v>
+        <v>0</v>
       </c>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="14" x14ac:dyDescent="0.3">
@@ -6557,13 +6557,13 @@
         <v>48</v>
       </c>
       <c r="B14" s="0">
-        <v>6.4354115378577081e-09</v>
+        <v>0</v>
       </c>
       <c r="C14" s="0">
-        <v>1.4917405790035879e-09</v>
+        <v>0</v>
       </c>
       <c r="D14" s="0">
-        <v>1.5043908583539175e-09</v>
+        <v>0</v>
       </c>
       <c r="E14" s="0">
         <v>0</v>
@@ -6575,7 +6575,7 @@
         <v>0</v>
       </c>
       <c r="H14" s="0">
-        <v>4.3890934412954242e-09</v>
+        <v>0</v>
       </c>
       <c r="I14" s="0">
         <v>0</v>
@@ -6584,7 +6584,7 @@
         <v>0</v>
       </c>
       <c r="K14" s="0">
-        <v>3.9930403285138614e-08</v>
+        <v>0</v>
       </c>
       <c r="L14" s="0">
         <v>0</v>
@@ -6599,22 +6599,22 @@
         <v>0</v>
       </c>
       <c r="P14" s="0">
-        <v>1.3781068110583784e-06</v>
+        <v>1.209327321325348e-06</v>
       </c>
       <c r="Q14" s="0">
-        <v>1.8248270154192629e-07</v>
+        <v>0</v>
       </c>
       <c r="R14" s="0">
-        <v>3.2312931117400845e-08</v>
+        <v>0</v>
       </c>
       <c r="S14" s="0">
-        <v>5.7990613300702181e-09</v>
+        <v>0</v>
       </c>
       <c r="T14" s="0">
-        <v>1.4731620100671334e-08</v>
+        <v>0</v>
       </c>
       <c r="U14" s="0">
-        <v>6.0213630429604592e-05</v>
+        <v>0</v>
       </c>
       <c r="V14" s="0">
         <v>0</v>
@@ -6623,19 +6623,19 @@
         <v>0</v>
       </c>
       <c r="X14" s="0">
-        <v>1.2995465118983588e-08</v>
+        <v>0</v>
       </c>
       <c r="Y14" s="0">
         <v>0</v>
       </c>
       <c r="Z14" s="0">
-        <v>3.6565134959642609e-07</v>
+        <v>0</v>
       </c>
       <c r="AA14" s="0">
-        <v>1.1714162820430389e-07</v>
+        <v>0</v>
       </c>
       <c r="AB14" s="0">
-        <v>7.651713045028221e-09</v>
+        <v>0</v>
       </c>
       <c r="AC14" s="0">
         <v>0</v>
@@ -6647,19 +6647,19 @@
         <v>0</v>
       </c>
       <c r="AF14" s="0">
-        <v>9.3010416066236412e-08</v>
+        <v>0</v>
       </c>
       <c r="AG14" s="0">
-        <v>1.8796925217107314e-06</v>
+        <v>2.7756184793013751e-06</v>
       </c>
       <c r="AH14" s="0">
         <v>0</v>
       </c>
       <c r="AI14" s="0">
-        <v>0</v>
+        <v>1.0727373270201461e-07</v>
       </c>
       <c r="AJ14" s="0">
-        <v>1.3891895215028436e-07</v>
+        <v>1.2891310516283422e-07</v>
       </c>
     </row>
   </sheetData>
@@ -6689,7 +6689,7 @@
         <v>7</v>
       </c>
       <c r="B2" s="0">
-        <v>0.16440559553183934</v>
+        <v>0.16616152051904118</v>
       </c>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="3" x14ac:dyDescent="0.3">
@@ -6697,7 +6697,7 @@
         <v>8</v>
       </c>
       <c r="B3" s="0">
-        <v>0.24266004534877847</v>
+        <v>0.24459453026737443</v>
       </c>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="4" x14ac:dyDescent="0.3">
@@ -6705,7 +6705,7 @@
         <v>9</v>
       </c>
       <c r="B4" s="0">
-        <v>0.27334455027435495</v>
+        <v>0.27676146357661585</v>
       </c>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="5" x14ac:dyDescent="0.3">
@@ -6713,7 +6713,7 @@
         <v>10</v>
       </c>
       <c r="B5" s="0">
-        <v>0.1925943968767716</v>
+        <v>0.19466993145920483</v>
       </c>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="6" x14ac:dyDescent="0.3">
@@ -6721,7 +6721,7 @@
         <v>11</v>
       </c>
       <c r="B6" s="0">
-        <v>0.24263593596617308</v>
+        <v>0.24494731481395951</v>
       </c>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="7" x14ac:dyDescent="0.3">
@@ -6729,7 +6729,7 @@
         <v>12</v>
       </c>
       <c r="B7" s="0">
-        <v>0.24770747623058137</v>
+        <v>0.25049989211510193</v>
       </c>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="8" x14ac:dyDescent="0.3">
@@ -6737,7 +6737,7 @@
         <v>13</v>
       </c>
       <c r="B8" s="0">
-        <v>0.063571439489240766</v>
+        <v>0.063481075128863446</v>
       </c>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="9" x14ac:dyDescent="0.3">
@@ -6745,7 +6745,7 @@
         <v>14</v>
       </c>
       <c r="B9" s="0">
-        <v>0.28382064380168182</v>
+        <v>0.2861402330185846</v>
       </c>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="10" x14ac:dyDescent="0.3">
@@ -6753,7 +6753,7 @@
         <v>15</v>
       </c>
       <c r="B10" s="0">
-        <v>0.28816999728436626</v>
+        <v>0.29137968650030582</v>
       </c>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="11" x14ac:dyDescent="0.3">
@@ -6761,7 +6761,7 @@
         <v>16</v>
       </c>
       <c r="B11" s="0">
-        <v>0.22094104345228865</v>
+        <v>0.22331392098636688</v>
       </c>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="12" x14ac:dyDescent="0.3">
@@ -6769,7 +6769,7 @@
         <v>17</v>
       </c>
       <c r="B12" s="0">
-        <v>0.2247378535319528</v>
+        <v>0.22725257698084725</v>
       </c>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="13" x14ac:dyDescent="0.3">
@@ -6795,7 +6795,7 @@
         <v>18</v>
       </c>
       <c r="B16" s="0">
-        <v>0.15934132868735451</v>
+        <v>0.15932288108080564</v>
       </c>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="17" x14ac:dyDescent="0.3">
@@ -6803,7 +6803,7 @@
         <v>19</v>
       </c>
       <c r="B17" s="0">
-        <v>0.23945378800471784</v>
+        <v>0.23816289838090338</v>
       </c>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="18" x14ac:dyDescent="0.3">
@@ -6811,7 +6811,7 @@
         <v>20</v>
       </c>
       <c r="B18" s="0">
-        <v>0.2388657925034664</v>
+        <v>0.23770114028341427</v>
       </c>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="19" x14ac:dyDescent="0.3">
@@ -6819,7 +6819,7 @@
         <v>21</v>
       </c>
       <c r="B19" s="0">
-        <v>0.0071928988825345277</v>
+        <v>0.0072123727126655879</v>
       </c>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="20" x14ac:dyDescent="0.3">
@@ -6827,7 +6827,7 @@
         <v>22</v>
       </c>
       <c r="B20" s="0">
-        <v>0.12477449352919197</v>
+        <v>0.12611070494401899</v>
       </c>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="21" x14ac:dyDescent="0.3">
@@ -6835,7 +6835,7 @@
         <v>23</v>
       </c>
       <c r="B21" s="0">
-        <v>0.14091284476445901</v>
+        <v>0.14269797371921344</v>
       </c>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="22" x14ac:dyDescent="0.3">
@@ -6843,7 +6843,7 @@
         <v>24</v>
       </c>
       <c r="B22" s="0">
-        <v>0.13507750723699213</v>
+        <v>0.14310104936459195</v>
       </c>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="23" x14ac:dyDescent="0.3">
@@ -6851,7 +6851,7 @@
         <v>25</v>
       </c>
       <c r="B23" s="0">
-        <v>0.0073500611831173387</v>
+        <v>0.0074075249274076936</v>
       </c>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="24" x14ac:dyDescent="0.3">
@@ -6859,7 +6859,7 @@
         <v>26</v>
       </c>
       <c r="B24" s="0">
-        <v>0.17379334743885547</v>
+        <v>0.17551843928900485</v>
       </c>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="25" x14ac:dyDescent="0.3">
@@ -6867,7 +6867,7 @@
         <v>27</v>
       </c>
       <c r="B25" s="0">
-        <v>0.20664956150731939</v>
+        <v>0.20881847615766278</v>
       </c>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="26" x14ac:dyDescent="0.3">
@@ -6875,7 +6875,7 @@
         <v>28</v>
       </c>
       <c r="B26" s="0">
-        <v>0.21481602529694985</v>
+        <v>0.21755813719807979</v>
       </c>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="27" x14ac:dyDescent="0.3">
@@ -6883,7 +6883,7 @@
         <v>29</v>
       </c>
       <c r="B27" s="0">
-        <v>0.15219298000345274</v>
+        <v>0.15363699585462146</v>
       </c>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="28" x14ac:dyDescent="0.3">
@@ -6891,7 +6891,7 @@
         <v>30</v>
       </c>
       <c r="B28" s="0">
-        <v>0.22196937530146027</v>
+        <v>0.22430248796252833</v>
       </c>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="29" x14ac:dyDescent="0.3">
@@ -6899,7 +6899,7 @@
         <v>31</v>
       </c>
       <c r="B29" s="0">
-        <v>0.2590701327920395</v>
+        <v>0.26149725576437771</v>
       </c>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="30" x14ac:dyDescent="0.3">
@@ -6907,7 +6907,7 @@
         <v>32</v>
       </c>
       <c r="B30" s="0">
-        <v>0.2593820304332532</v>
+        <v>0.26222196916459506</v>
       </c>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="31" x14ac:dyDescent="0.3">
@@ -6915,7 +6915,7 @@
         <v>33</v>
       </c>
       <c r="B31" s="0">
-        <v>0.15098185677285647</v>
+        <v>0.15374570556766803</v>
       </c>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="32" x14ac:dyDescent="0.3">
